--- a/playoffs-example-medium-seeded.xlsx
+++ b/playoffs-example-medium-seeded.xlsx
@@ -892,11 +892,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="15"/>
-    <col customWidth="true" max="26" min="2" width="30"/>
+    <col customWidth="true" max="1" min="1" width="9"/>
+    <col customWidth="true" max="3" min="2" width="20"/>
+    <col customWidth="true" max="26" min="4" width="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1261,7 +1265,8 @@
       </c>
     </row>
   </sheetData>
-  <pageSetup orientation="landscape"/>
+  <printOptions horizontalCentered="true" verticalCentered="true"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -2816,7 +2821,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="20.83"/>
+    <col customWidth="true" max="1" min="1" width="25"/>
     <col customWidth="true" max="2" min="2" width="10"/>
     <col customWidth="true" max="26" min="3" width="3.5"/>
   </cols>
@@ -3048,7 +3053,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="20.83"/>
+    <col customWidth="true" max="1" min="1" width="25"/>
     <col customWidth="true" max="2" min="2" width="10"/>
     <col customWidth="true" max="26" min="3" width="3.5"/>
   </cols>

--- a/playoffs-example-medium-seeded.xlsx
+++ b/playoffs-example-medium-seeded.xlsx
@@ -10,12 +10,14 @@
     <sheet name="data" sheetId="1" r:id="rId1"/>
     <sheet name="Time Estimator" sheetId="2" r:id="rId4"/>
     <sheet name="Elimination Matches" sheetId="5" r:id="rId7"/>
-    <sheet name="Names to Print" sheetId="6" r:id="rId8"/>
     <sheet name="Tree 1" sheetId="8" r:id="rId11"/>
     <sheet name="Tree 2" sheetId="9" r:id="rId12"/>
+    <sheet name="Names to Print A" sheetId="10" r:id="rId13"/>
+    <sheet name="Names to Print B" sheetId="11" r:id="rId14"/>
   </sheets>
   <definedNames>
-    <definedName localSheetId="3" name="_xlnm.Print_Area">'Names to Print'!$A$1:$B$24</definedName>
+    <definedName localSheetId="5" name="_xlnm.Print_Area">'Names to Print A'!$A$1:$B$12</definedName>
+    <definedName localSheetId="6" name="_xlnm.Print_Area">'Names to Print B'!$A$1:$B$12</definedName>
     <definedName localSheetId="2" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$O$122</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
@@ -364,7 +366,7 @@
     <t>Round 4 - Match 22</t>
   </si>
   <si>
-    <t>Round 5 - Match 0</t>
+    <t>Round 5 - Match 23</t>
   </si>
   <si>
     <t>Tournament Summary</t>
@@ -1270,6 +1272,240 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
+    <col customWidth="true" max="1" min="1" width="30"/>
+    <col customWidth="true" max="2" min="2" width="160"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="270" customHeight="true">
+      <c r="A1" s="17">
+        <v>0</v>
+      </c>
+      <c r="B1" s="18" t="str">
+        <f>data!D3</f>
+      </c>
+    </row>
+    <row r="2" ht="270" customHeight="true">
+      <c r="A2" s="17">
+        <v>4</v>
+      </c>
+      <c r="B2" s="18" t="str">
+        <f>data!D7</f>
+      </c>
+    </row>
+    <row r="3" ht="270" customHeight="true">
+      <c r="A3" s="17">
+        <v>5</v>
+      </c>
+      <c r="B3" s="18" t="str">
+        <f>data!D8</f>
+      </c>
+    </row>
+    <row r="4" ht="270" customHeight="true">
+      <c r="A4" s="17">
+        <v>6</v>
+      </c>
+      <c r="B4" s="18" t="str">
+        <f>data!D9</f>
+      </c>
+    </row>
+    <row r="5" ht="270" customHeight="true">
+      <c r="A5" s="17">
+        <v>7</v>
+      </c>
+      <c r="B5" s="18" t="str">
+        <f>data!D10</f>
+      </c>
+    </row>
+    <row r="6" ht="270" customHeight="true">
+      <c r="A6" s="17">
+        <v>8</v>
+      </c>
+      <c r="B6" s="18" t="str">
+        <f>data!D11</f>
+      </c>
+    </row>
+    <row r="7" ht="270" customHeight="true">
+      <c r="A7" s="17">
+        <v>9</v>
+      </c>
+      <c r="B7" s="18" t="str">
+        <f>data!D12</f>
+      </c>
+    </row>
+    <row r="8" ht="270" customHeight="true">
+      <c r="A8" s="17">
+        <v>10</v>
+      </c>
+      <c r="B8" s="18" t="str">
+        <f>data!D13</f>
+      </c>
+    </row>
+    <row r="9" ht="270" customHeight="true">
+      <c r="A9" s="17">
+        <v>3</v>
+      </c>
+      <c r="B9" s="18" t="str">
+        <f>data!D6</f>
+      </c>
+    </row>
+    <row r="10" ht="270" customHeight="true">
+      <c r="A10" s="17">
+        <v>11</v>
+      </c>
+      <c r="B10" s="18" t="str">
+        <f>data!D14</f>
+      </c>
+    </row>
+    <row r="11" ht="270" customHeight="true">
+      <c r="A11" s="17">
+        <v>12</v>
+      </c>
+      <c r="B11" s="18" t="str">
+        <f>data!D15</f>
+      </c>
+    </row>
+    <row r="12" ht="270" customHeight="true">
+      <c r="A12" s="17">
+        <v>13</v>
+      </c>
+      <c r="B12" s="18" t="str">
+        <f>data!D16</f>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="8"/>
+  <rowBreaks count="4" manualBreakCount="4">
+    <brk id="3" max="16383" man="true"/>
+    <brk id="6" max="16383" man="true"/>
+    <brk id="9" max="16383" man="true"/>
+    <brk id="12" max="16383" man="true"/>
+  </rowBreaks>
+  <colBreaks/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
+    <col customWidth="true" max="1" min="1" width="30"/>
+    <col customWidth="true" max="2" min="2" width="160"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="270" customHeight="true">
+      <c r="A1" s="17">
+        <v>14</v>
+      </c>
+      <c r="B1" s="18" t="str">
+        <f>data!D17</f>
+      </c>
+    </row>
+    <row r="2" ht="270" customHeight="true">
+      <c r="A2" s="17">
+        <v>15</v>
+      </c>
+      <c r="B2" s="18" t="str">
+        <f>data!D18</f>
+      </c>
+    </row>
+    <row r="3" ht="270" customHeight="true">
+      <c r="A3" s="17">
+        <v>16</v>
+      </c>
+      <c r="B3" s="18" t="str">
+        <f>data!D19</f>
+      </c>
+    </row>
+    <row r="4" ht="270" customHeight="true">
+      <c r="A4" s="17">
+        <v>17</v>
+      </c>
+      <c r="B4" s="18" t="str">
+        <f>data!D20</f>
+      </c>
+    </row>
+    <row r="5" ht="270" customHeight="true">
+      <c r="A5" s="17">
+        <v>1</v>
+      </c>
+      <c r="B5" s="18" t="str">
+        <f>data!D4</f>
+      </c>
+    </row>
+    <row r="6" ht="270" customHeight="true">
+      <c r="A6" s="17">
+        <v>18</v>
+      </c>
+      <c r="B6" s="18" t="str">
+        <f>data!D21</f>
+      </c>
+    </row>
+    <row r="7" ht="270" customHeight="true">
+      <c r="A7" s="17">
+        <v>19</v>
+      </c>
+      <c r="B7" s="18" t="str">
+        <f>data!D22</f>
+      </c>
+    </row>
+    <row r="8" ht="270" customHeight="true">
+      <c r="A8" s="17">
+        <v>20</v>
+      </c>
+      <c r="B8" s="18" t="str">
+        <f>data!D23</f>
+      </c>
+    </row>
+    <row r="9" ht="270" customHeight="true">
+      <c r="A9" s="17">
+        <v>21</v>
+      </c>
+      <c r="B9" s="18" t="str">
+        <f>data!D24</f>
+      </c>
+    </row>
+    <row r="10" ht="270" customHeight="true">
+      <c r="A10" s="17">
+        <v>22</v>
+      </c>
+      <c r="B10" s="18" t="str">
+        <f>data!D25</f>
+      </c>
+    </row>
+    <row r="11" ht="270" customHeight="true">
+      <c r="A11" s="17">
+        <v>23</v>
+      </c>
+      <c r="B11" s="18" t="str">
+        <f>data!D26</f>
+      </c>
+    </row>
+    <row r="12" ht="270" customHeight="true">
+      <c r="A12" s="17">
+        <v>2</v>
+      </c>
+      <c r="B12" s="18" t="str">
+        <f>data!D5</f>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="8"/>
+  <rowBreaks count="4" manualBreakCount="4">
+    <brk id="3" max="16383" man="true"/>
+    <brk id="6" max="16383" man="true"/>
+    <brk id="9" max="16383" man="true"/>
+    <brk id="12" max="16383" man="true"/>
+  </rowBreaks>
+  <colBreaks/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
@@ -2600,223 +2836,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
-  <cols>
-    <col customWidth="true" max="1" min="1" style="9" width="30"/>
-    <col customWidth="true" max="2" min="2" style="10" width="160"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="270" customHeight="true">
-      <c r="A1" s="17">
-        <v>0</v>
-      </c>
-      <c r="B1" s="18" t="str">
-        <f>data!D3</f>
-      </c>
-    </row>
-    <row r="2" ht="270" customHeight="true">
-      <c r="A2" s="17">
-        <v>4</v>
-      </c>
-      <c r="B2" s="18" t="str">
-        <f>data!D7</f>
-      </c>
-    </row>
-    <row r="3" ht="270" customHeight="true">
-      <c r="A3" s="17">
-        <v>5</v>
-      </c>
-      <c r="B3" s="18" t="str">
-        <f>data!D8</f>
-      </c>
-    </row>
-    <row r="4" ht="270" customHeight="true">
-      <c r="A4" s="17">
-        <v>6</v>
-      </c>
-      <c r="B4" s="18" t="str">
-        <f>data!D9</f>
-      </c>
-    </row>
-    <row r="5" ht="270" customHeight="true">
-      <c r="A5" s="17">
-        <v>7</v>
-      </c>
-      <c r="B5" s="18" t="str">
-        <f>data!D10</f>
-      </c>
-    </row>
-    <row r="6" ht="270" customHeight="true">
-      <c r="A6" s="17">
-        <v>8</v>
-      </c>
-      <c r="B6" s="18" t="str">
-        <f>data!D11</f>
-      </c>
-    </row>
-    <row r="7" ht="270" customHeight="true">
-      <c r="A7" s="17">
-        <v>9</v>
-      </c>
-      <c r="B7" s="18" t="str">
-        <f>data!D12</f>
-      </c>
-    </row>
-    <row r="8" ht="270" customHeight="true">
-      <c r="A8" s="17">
-        <v>10</v>
-      </c>
-      <c r="B8" s="18" t="str">
-        <f>data!D13</f>
-      </c>
-    </row>
-    <row r="9" ht="270" customHeight="true">
-      <c r="A9" s="17">
-        <v>3</v>
-      </c>
-      <c r="B9" s="18" t="str">
-        <f>data!D6</f>
-      </c>
-    </row>
-    <row r="10" ht="270" customHeight="true">
-      <c r="A10" s="17">
-        <v>11</v>
-      </c>
-      <c r="B10" s="18" t="str">
-        <f>data!D14</f>
-      </c>
-    </row>
-    <row r="11" ht="270" customHeight="true">
-      <c r="A11" s="17">
-        <v>12</v>
-      </c>
-      <c r="B11" s="18" t="str">
-        <f>data!D15</f>
-      </c>
-    </row>
-    <row r="12" ht="270" customHeight="true">
-      <c r="A12" s="17">
-        <v>13</v>
-      </c>
-      <c r="B12" s="18" t="str">
-        <f>data!D16</f>
-      </c>
-    </row>
-    <row r="13" ht="270" customHeight="true">
-      <c r="A13" s="17">
-        <v>14</v>
-      </c>
-      <c r="B13" s="18" t="str">
-        <f>data!D17</f>
-      </c>
-    </row>
-    <row r="14" ht="270" customHeight="true">
-      <c r="A14" s="17">
-        <v>15</v>
-      </c>
-      <c r="B14" s="18" t="str">
-        <f>data!D18</f>
-      </c>
-    </row>
-    <row r="15" ht="270" customHeight="true">
-      <c r="A15" s="17">
-        <v>16</v>
-      </c>
-      <c r="B15" s="18" t="str">
-        <f>data!D19</f>
-      </c>
-    </row>
-    <row r="16" ht="270" customHeight="true">
-      <c r="A16" s="17">
-        <v>17</v>
-      </c>
-      <c r="B16" s="18" t="str">
-        <f>data!D20</f>
-      </c>
-    </row>
-    <row r="17" ht="270" customHeight="true">
-      <c r="A17" s="17">
-        <v>1</v>
-      </c>
-      <c r="B17" s="18" t="str">
-        <f>data!D4</f>
-      </c>
-    </row>
-    <row r="18" ht="270" customHeight="true">
-      <c r="A18" s="17">
-        <v>18</v>
-      </c>
-      <c r="B18" s="18" t="str">
-        <f>data!D21</f>
-      </c>
-    </row>
-    <row r="19" ht="270" customHeight="true">
-      <c r="A19" s="17">
-        <v>19</v>
-      </c>
-      <c r="B19" s="18" t="str">
-        <f>data!D22</f>
-      </c>
-    </row>
-    <row r="20" ht="270" customHeight="true">
-      <c r="A20" s="17">
-        <v>20</v>
-      </c>
-      <c r="B20" s="18" t="str">
-        <f>data!D23</f>
-      </c>
-    </row>
-    <row r="21" ht="270" customHeight="true">
-      <c r="A21" s="17">
-        <v>21</v>
-      </c>
-      <c r="B21" s="18" t="str">
-        <f>data!D24</f>
-      </c>
-    </row>
-    <row r="22" ht="270" customHeight="true">
-      <c r="A22" s="17">
-        <v>22</v>
-      </c>
-      <c r="B22" s="18" t="str">
-        <f>data!D25</f>
-      </c>
-    </row>
-    <row r="23" ht="270" customHeight="true">
-      <c r="A23" s="17">
-        <v>23</v>
-      </c>
-      <c r="B23" s="18" t="str">
-        <f>data!D26</f>
-      </c>
-    </row>
-    <row r="24" ht="270" customHeight="true">
-      <c r="A24" s="17">
-        <v>2</v>
-      </c>
-      <c r="B24" s="18" t="str">
-        <f>data!D5</f>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="8"/>
-  <rowBreaks count="8" manualBreakCount="8">
-    <brk id="3" max="16383" man="true"/>
-    <brk id="6" max="16383" man="true"/>
-    <brk id="9" max="16383" man="true"/>
-    <brk id="12" max="16383" man="true"/>
-    <brk id="15" max="16383" man="true"/>
-    <brk id="18" max="16383" man="true"/>
-    <brk id="21" max="16383" man="true"/>
-    <brk id="24" max="16383" man="true"/>
-  </rowBreaks>
-  <colBreaks/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>

--- a/playoffs-example-medium-seeded.xlsx
+++ b/playoffs-example-medium-seeded.xlsx
@@ -475,12 +475,17 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFEFEF"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -556,7 +561,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
@@ -603,7 +608,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
@@ -612,16 +617,27 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center"/>
+      <protection hidden="false" locked="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment/>
+      <protection hidden="false" locked="false"/>
+    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="20" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
@@ -1377,6 +1393,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="8"/>
   <rowBreaks count="4" manualBreakCount="4">
@@ -1494,6 +1511,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="8"/>
   <rowBreaks count="4" manualBreakCount="4">
@@ -1566,7 +1584,7 @@
       <c r="G2" s="3">
         <v>0.020833333333333332</v>
       </c>
-      <c r="H2" s="22" t="str">
+      <c r="H2" s="24" t="str">
         <f>C2*I2+J2</f>
       </c>
     </row>
@@ -1670,7 +1688,7 @@
       <c r="G8" s="3">
         <v>0.020833333333333332</v>
       </c>
-      <c r="H8" s="22" t="str">
+      <c r="H8" s="24" t="str">
         <f>E8+(A8*F8)+G8</f>
       </c>
     </row>
@@ -1716,42 +1734,42 @@
       <c r="A14">
         <v>2</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="E14" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="22" t="str">
+      <c r="F14" s="25"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="24" t="str">
         <f>H2</f>
       </c>
     </row>
     <row r="15">
-      <c r="E15" s="19" t="s">
+      <c r="E15" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="22" t="str">
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="24" t="str">
         <f>H8</f>
       </c>
     </row>
     <row r="16">
-      <c r="E16" s="19" t="s">
+      <c r="E16" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="22" t="str">
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="24" t="str">
         <f>H14+H15</f>
       </c>
     </row>
     <row r="17">
-      <c r="E17" s="19" t="s">
+      <c r="E17" s="25" t="s">
         <v>118</v>
       </c>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="22" t="str">
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="24" t="str">
         <f>H16/A14</f>
       </c>
     </row>
@@ -1761,7 +1779,7 @@
       </c>
       <c r="F18" s="11"/>
       <c r="G18" s="11"/>
-      <c r="H18" s="23">
+      <c r="H18" s="26">
         <v>0.375</v>
       </c>
     </row>
@@ -1771,7 +1789,7 @@
       </c>
       <c r="F19" s="11"/>
       <c r="G19" s="11"/>
-      <c r="H19" s="23" t="str">
+      <c r="H19" s="26" t="str">
         <f>H18+H17</f>
       </c>
     </row>
@@ -1795,14 +1813,15 @@
     <col customWidth="true" max="4" min="4" width="3"/>
     <col customWidth="true" max="6" min="5" width="5"/>
     <col customWidth="true" max="7" min="7" width="30"/>
-    <col customWidth="true" max="8" min="8" width="2"/>
+    <col customWidth="true" max="8" min="8" width="5"/>
     <col customWidth="true" max="9" min="9" width="30"/>
     <col customWidth="true" max="11" min="10" width="5"/>
     <col customWidth="true" max="12" min="12" width="3"/>
     <col customWidth="true" max="14" min="13" width="5"/>
     <col customWidth="true" max="15" min="15" width="30"/>
-    <col customWidth="true" max="16" min="16" width="2"/>
-    <col customWidth="true" max="20" min="17" width="10.83"/>
+    <col customWidth="true" max="18" min="16" width="5"/>
+    <col customWidth="true" max="19" min="19" width="30"/>
+    <col customWidth="true" max="20" min="20" width="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1869,22 +1888,22 @@
       <c r="A4" s="19" t="str">
         <f>'data'!$B$8</f>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
       <c r="G4" s="19" t="str">
         <f>'data'!$B$7</f>
       </c>
       <c r="I4" s="19" t="str">
         <f>'data'!$B$19</f>
       </c>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="19"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
       <c r="O4" s="19" t="str">
         <f>'data'!$B$18</f>
       </c>
@@ -1893,21 +1912,21 @@
       <c r="F6" t="s">
         <v>90</v>
       </c>
-      <c r="G6" s="15"/>
+      <c r="G6" s="23"/>
       <c r="N6" t="s">
         <v>90</v>
       </c>
-      <c r="O6" s="15"/>
+      <c r="O6" s="23"/>
     </row>
     <row r="7">
       <c r="F7" t="s">
         <v>91</v>
       </c>
-      <c r="G7" s="15"/>
+      <c r="G7" s="23"/>
       <c r="N7" t="s">
         <v>91</v>
       </c>
-      <c r="O7" s="15"/>
+      <c r="O7" s="23"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="s">
@@ -1953,22 +1972,22 @@
       <c r="A12" s="19" t="str">
         <f>'data'!$B$12</f>
       </c>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="22"/>
       <c r="G12" s="19" t="str">
         <f>'data'!$B$10</f>
       </c>
       <c r="I12" s="19" t="str">
         <f>'data'!$B$21</f>
       </c>
-      <c r="J12" s="19"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="19"/>
-      <c r="M12" s="19"/>
-      <c r="N12" s="19"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="22"/>
+      <c r="M12" s="22"/>
+      <c r="N12" s="22"/>
       <c r="O12" s="19" t="str">
         <f>'data'!$B$4</f>
       </c>
@@ -1977,21 +1996,21 @@
       <c r="F14" t="s">
         <v>90</v>
       </c>
-      <c r="G14" s="15"/>
+      <c r="G14" s="23"/>
       <c r="N14" t="s">
         <v>90</v>
       </c>
-      <c r="O14" s="15"/>
+      <c r="O14" s="23"/>
     </row>
     <row r="15">
       <c r="F15" t="s">
         <v>91</v>
       </c>
-      <c r="G15" s="15"/>
+      <c r="G15" s="23"/>
       <c r="N15" t="s">
         <v>91</v>
       </c>
-      <c r="O15" s="15"/>
+      <c r="O15" s="23"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="s">
@@ -2037,22 +2056,22 @@
       <c r="A20" s="19" t="str">
         <f>'data'!$B$6</f>
       </c>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
       <c r="G20" s="19" t="str">
         <f>'data'!$B$13</f>
       </c>
       <c r="I20" s="19" t="str">
         <f>'data'!$B$24</f>
       </c>
-      <c r="J20" s="19"/>
-      <c r="K20" s="19"/>
-      <c r="L20" s="19"/>
-      <c r="M20" s="19"/>
-      <c r="N20" s="19"/>
+      <c r="J20" s="22"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="22"/>
+      <c r="M20" s="22"/>
+      <c r="N20" s="22"/>
       <c r="O20" s="19" t="str">
         <f>'data'!$B$23</f>
       </c>
@@ -2061,21 +2080,21 @@
       <c r="F22" t="s">
         <v>90</v>
       </c>
-      <c r="G22" s="15"/>
+      <c r="G22" s="23"/>
       <c r="N22" t="s">
         <v>90</v>
       </c>
-      <c r="O22" s="15"/>
+      <c r="O22" s="23"/>
     </row>
     <row r="23">
       <c r="F23" t="s">
         <v>91</v>
       </c>
-      <c r="G23" s="15"/>
+      <c r="G23" s="23"/>
       <c r="N23" t="s">
         <v>91</v>
       </c>
-      <c r="O23" s="15"/>
+      <c r="O23" s="23"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="s">
@@ -2121,22 +2140,22 @@
       <c r="A28" s="19" t="str">
         <f>'data'!$B$16</f>
       </c>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
+      <c r="B28" s="22"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
       <c r="G28" s="19" t="str">
         <f>'data'!$B$15</f>
       </c>
       <c r="I28" s="19" t="str">
         <f>'data'!$B$5</f>
       </c>
-      <c r="J28" s="19"/>
-      <c r="K28" s="19"/>
-      <c r="L28" s="19"/>
-      <c r="M28" s="19"/>
-      <c r="N28" s="19"/>
+      <c r="J28" s="22"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="22"/>
+      <c r="M28" s="22"/>
+      <c r="N28" s="22"/>
       <c r="O28" s="19" t="str">
         <f>'data'!$B$26</f>
       </c>
@@ -2145,21 +2164,21 @@
       <c r="F30" t="s">
         <v>90</v>
       </c>
-      <c r="G30" s="15"/>
+      <c r="G30" s="23"/>
       <c r="N30" t="s">
         <v>90</v>
       </c>
-      <c r="O30" s="15"/>
+      <c r="O30" s="23"/>
     </row>
     <row r="31">
       <c r="F31" t="s">
         <v>91</v>
       </c>
-      <c r="G31" s="15"/>
+      <c r="G31" s="23"/>
       <c r="N31" t="s">
         <v>91</v>
       </c>
-      <c r="O31" s="15"/>
+      <c r="O31" s="23"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="s">
@@ -2205,22 +2224,22 @@
       <c r="A41" s="19" t="str">
         <f>CONCATENATE("M 1 ",G6)</f>
       </c>
-      <c r="B41" s="19"/>
-      <c r="C41" s="19"/>
-      <c r="D41" s="19"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="19"/>
+      <c r="B41" s="22"/>
+      <c r="C41" s="22"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="22"/>
       <c r="G41" s="19" t="str">
         <f>'data'!$B$21</f>
       </c>
       <c r="I41" s="19" t="str">
         <f>CONCATENATE("M 5 ",O6)</f>
       </c>
-      <c r="J41" s="19"/>
-      <c r="K41" s="19"/>
-      <c r="L41" s="19"/>
-      <c r="M41" s="19"/>
-      <c r="N41" s="19"/>
+      <c r="J41" s="22"/>
+      <c r="K41" s="22"/>
+      <c r="L41" s="22"/>
+      <c r="M41" s="22"/>
+      <c r="N41" s="22"/>
       <c r="O41" s="19" t="str">
         <f>'data'!$B$17</f>
       </c>
@@ -2229,21 +2248,21 @@
       <c r="F43" t="s">
         <v>90</v>
       </c>
-      <c r="G43" s="15"/>
+      <c r="G43" s="23"/>
       <c r="N43" t="s">
         <v>90</v>
       </c>
-      <c r="O43" s="15"/>
+      <c r="O43" s="23"/>
     </row>
     <row r="44">
       <c r="F44" t="s">
         <v>91</v>
       </c>
-      <c r="G44" s="15"/>
+      <c r="G44" s="23"/>
       <c r="N44" t="s">
         <v>91</v>
       </c>
-      <c r="O44" s="15"/>
+      <c r="O44" s="23"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="s">
@@ -2289,22 +2308,22 @@
       <c r="A49" s="19" t="str">
         <f>CONCATENATE("M 2 ",G14)</f>
       </c>
-      <c r="B49" s="19"/>
-      <c r="C49" s="19"/>
-      <c r="D49" s="19"/>
-      <c r="E49" s="19"/>
-      <c r="F49" s="19"/>
+      <c r="B49" s="22"/>
+      <c r="C49" s="22"/>
+      <c r="D49" s="22"/>
+      <c r="E49" s="22"/>
+      <c r="F49" s="22"/>
       <c r="G49" s="19" t="str">
         <f>'data'!$B$9</f>
       </c>
       <c r="I49" s="19" t="str">
         <f>CONCATENATE("M 6 ",O14)</f>
       </c>
-      <c r="J49" s="19"/>
-      <c r="K49" s="19"/>
-      <c r="L49" s="19"/>
-      <c r="M49" s="19"/>
-      <c r="N49" s="19"/>
+      <c r="J49" s="22"/>
+      <c r="K49" s="22"/>
+      <c r="L49" s="22"/>
+      <c r="M49" s="22"/>
+      <c r="N49" s="22"/>
       <c r="O49" s="19" t="str">
         <f>'data'!$B$20</f>
       </c>
@@ -2313,21 +2332,21 @@
       <c r="F51" t="s">
         <v>90</v>
       </c>
-      <c r="G51" s="15"/>
+      <c r="G51" s="23"/>
       <c r="N51" t="s">
         <v>90</v>
       </c>
-      <c r="O51" s="15"/>
+      <c r="O51" s="23"/>
     </row>
     <row r="52">
       <c r="F52" t="s">
         <v>91</v>
       </c>
-      <c r="G52" s="15"/>
+      <c r="G52" s="23"/>
       <c r="N52" t="s">
         <v>91</v>
       </c>
-      <c r="O52" s="15"/>
+      <c r="O52" s="23"/>
     </row>
     <row r="55">
       <c r="A55" s="11" t="s">
@@ -2373,22 +2392,22 @@
       <c r="A57" s="19" t="str">
         <f>CONCATENATE("M 3 ",G22)</f>
       </c>
-      <c r="B57" s="19"/>
-      <c r="C57" s="19"/>
-      <c r="D57" s="19"/>
-      <c r="E57" s="19"/>
-      <c r="F57" s="19"/>
+      <c r="B57" s="22"/>
+      <c r="C57" s="22"/>
+      <c r="D57" s="22"/>
+      <c r="E57" s="22"/>
+      <c r="F57" s="22"/>
       <c r="G57" s="19" t="str">
         <f>'data'!$B$12</f>
       </c>
       <c r="I57" s="19" t="str">
         <f>CONCATENATE("M 7 ",O22)</f>
       </c>
-      <c r="J57" s="19"/>
-      <c r="K57" s="19"/>
-      <c r="L57" s="19"/>
-      <c r="M57" s="19"/>
-      <c r="N57" s="19"/>
+      <c r="J57" s="22"/>
+      <c r="K57" s="22"/>
+      <c r="L57" s="22"/>
+      <c r="M57" s="22"/>
+      <c r="N57" s="22"/>
       <c r="O57" s="19" t="str">
         <f>'data'!$B$22</f>
       </c>
@@ -2397,21 +2416,21 @@
       <c r="F59" t="s">
         <v>90</v>
       </c>
-      <c r="G59" s="15"/>
+      <c r="G59" s="23"/>
       <c r="N59" t="s">
         <v>90</v>
       </c>
-      <c r="O59" s="15"/>
+      <c r="O59" s="23"/>
     </row>
     <row r="60">
       <c r="F60" t="s">
         <v>91</v>
       </c>
-      <c r="G60" s="15"/>
+      <c r="G60" s="23"/>
       <c r="N60" t="s">
         <v>91</v>
       </c>
-      <c r="O60" s="15"/>
+      <c r="O60" s="23"/>
     </row>
     <row r="63">
       <c r="A63" s="11" t="s">
@@ -2457,22 +2476,22 @@
       <c r="A65" s="19" t="str">
         <f>CONCATENATE("M 4 ",G30)</f>
       </c>
-      <c r="B65" s="19"/>
-      <c r="C65" s="19"/>
-      <c r="D65" s="19"/>
-      <c r="E65" s="19"/>
-      <c r="F65" s="19"/>
+      <c r="B65" s="22"/>
+      <c r="C65" s="22"/>
+      <c r="D65" s="22"/>
+      <c r="E65" s="22"/>
+      <c r="F65" s="22"/>
       <c r="G65" s="19" t="str">
         <f>'data'!$B$14</f>
       </c>
       <c r="I65" s="19" t="str">
         <f>CONCATENATE("M 8 ",O30)</f>
       </c>
-      <c r="J65" s="19"/>
-      <c r="K65" s="19"/>
-      <c r="L65" s="19"/>
-      <c r="M65" s="19"/>
-      <c r="N65" s="19"/>
+      <c r="J65" s="22"/>
+      <c r="K65" s="22"/>
+      <c r="L65" s="22"/>
+      <c r="M65" s="22"/>
+      <c r="N65" s="22"/>
       <c r="O65" s="19" t="str">
         <f>'data'!$B$25</f>
       </c>
@@ -2481,21 +2500,21 @@
       <c r="F67" t="s">
         <v>90</v>
       </c>
-      <c r="G67" s="15"/>
+      <c r="G67" s="23"/>
       <c r="N67" t="s">
         <v>90</v>
       </c>
-      <c r="O67" s="15"/>
+      <c r="O67" s="23"/>
     </row>
     <row r="68">
       <c r="F68" t="s">
         <v>91</v>
       </c>
-      <c r="G68" s="15"/>
+      <c r="G68" s="23"/>
       <c r="N68" t="s">
         <v>91</v>
       </c>
-      <c r="O68" s="15"/>
+      <c r="O68" s="23"/>
     </row>
     <row r="76">
       <c r="A76" s="11" t="s">
@@ -2541,22 +2560,22 @@
       <c r="A78" s="19" t="str">
         <f>CONCATENATE("M 10 ",G51)</f>
       </c>
-      <c r="B78" s="19"/>
-      <c r="C78" s="19"/>
-      <c r="D78" s="19"/>
-      <c r="E78" s="19"/>
-      <c r="F78" s="19"/>
+      <c r="B78" s="22"/>
+      <c r="C78" s="22"/>
+      <c r="D78" s="22"/>
+      <c r="E78" s="22"/>
+      <c r="F78" s="22"/>
       <c r="G78" s="19" t="str">
         <f>CONCATENATE("M 9 ",G43)</f>
       </c>
       <c r="I78" s="19" t="str">
         <f>CONCATENATE("M 14 ",O51)</f>
       </c>
-      <c r="J78" s="19"/>
-      <c r="K78" s="19"/>
-      <c r="L78" s="19"/>
-      <c r="M78" s="19"/>
-      <c r="N78" s="19"/>
+      <c r="J78" s="22"/>
+      <c r="K78" s="22"/>
+      <c r="L78" s="22"/>
+      <c r="M78" s="22"/>
+      <c r="N78" s="22"/>
       <c r="O78" s="19" t="str">
         <f>CONCATENATE("M 13 ",O43)</f>
       </c>
@@ -2565,21 +2584,21 @@
       <c r="F80" t="s">
         <v>90</v>
       </c>
-      <c r="G80" s="15"/>
+      <c r="G80" s="23"/>
       <c r="N80" t="s">
         <v>90</v>
       </c>
-      <c r="O80" s="15"/>
+      <c r="O80" s="23"/>
     </row>
     <row r="81">
       <c r="F81" t="s">
         <v>91</v>
       </c>
-      <c r="G81" s="15"/>
+      <c r="G81" s="23"/>
       <c r="N81" t="s">
         <v>91</v>
       </c>
-      <c r="O81" s="15"/>
+      <c r="O81" s="23"/>
     </row>
     <row r="84">
       <c r="A84" s="11" t="s">
@@ -2625,22 +2644,22 @@
       <c r="A86" s="19" t="str">
         <f>CONCATENATE("M 12 ",G67)</f>
       </c>
-      <c r="B86" s="19"/>
-      <c r="C86" s="19"/>
-      <c r="D86" s="19"/>
-      <c r="E86" s="19"/>
-      <c r="F86" s="19"/>
+      <c r="B86" s="22"/>
+      <c r="C86" s="22"/>
+      <c r="D86" s="22"/>
+      <c r="E86" s="22"/>
+      <c r="F86" s="22"/>
       <c r="G86" s="19" t="str">
         <f>CONCATENATE("M 11 ",G59)</f>
       </c>
       <c r="I86" s="19" t="str">
         <f>CONCATENATE("M 16 ",O67)</f>
       </c>
-      <c r="J86" s="19"/>
-      <c r="K86" s="19"/>
-      <c r="L86" s="19"/>
-      <c r="M86" s="19"/>
-      <c r="N86" s="19"/>
+      <c r="J86" s="22"/>
+      <c r="K86" s="22"/>
+      <c r="L86" s="22"/>
+      <c r="M86" s="22"/>
+      <c r="N86" s="22"/>
       <c r="O86" s="19" t="str">
         <f>CONCATENATE("M 15 ",O59)</f>
       </c>
@@ -2649,21 +2668,21 @@
       <c r="F88" t="s">
         <v>90</v>
       </c>
-      <c r="G88" s="15"/>
+      <c r="G88" s="23"/>
       <c r="N88" t="s">
         <v>90</v>
       </c>
-      <c r="O88" s="15"/>
+      <c r="O88" s="23"/>
     </row>
     <row r="89">
       <c r="F89" t="s">
         <v>91</v>
       </c>
-      <c r="G89" s="15"/>
+      <c r="G89" s="23"/>
       <c r="N89" t="s">
         <v>91</v>
       </c>
-      <c r="O89" s="15"/>
+      <c r="O89" s="23"/>
     </row>
     <row r="97">
       <c r="A97" s="11" t="s">
@@ -2709,22 +2728,22 @@
       <c r="A99" s="19" t="str">
         <f>CONCATENATE("M 18 ",G88)</f>
       </c>
-      <c r="B99" s="19"/>
-      <c r="C99" s="19"/>
-      <c r="D99" s="19"/>
-      <c r="E99" s="19"/>
-      <c r="F99" s="19"/>
+      <c r="B99" s="22"/>
+      <c r="C99" s="22"/>
+      <c r="D99" s="22"/>
+      <c r="E99" s="22"/>
+      <c r="F99" s="22"/>
       <c r="G99" s="19" t="str">
         <f>CONCATENATE("M 17 ",G80)</f>
       </c>
       <c r="I99" s="19" t="str">
         <f>CONCATENATE("M 20 ",O88)</f>
       </c>
-      <c r="J99" s="19"/>
-      <c r="K99" s="19"/>
-      <c r="L99" s="19"/>
-      <c r="M99" s="19"/>
-      <c r="N99" s="19"/>
+      <c r="J99" s="22"/>
+      <c r="K99" s="22"/>
+      <c r="L99" s="22"/>
+      <c r="M99" s="22"/>
+      <c r="N99" s="22"/>
       <c r="O99" s="19" t="str">
         <f>CONCATENATE("M 19 ",O80)</f>
       </c>
@@ -2733,21 +2752,21 @@
       <c r="F101" t="s">
         <v>90</v>
       </c>
-      <c r="G101" s="15"/>
+      <c r="G101" s="23"/>
       <c r="N101" t="s">
         <v>90</v>
       </c>
-      <c r="O101" s="15"/>
+      <c r="O101" s="23"/>
     </row>
     <row r="102">
       <c r="F102" t="s">
         <v>91</v>
       </c>
-      <c r="G102" s="15"/>
+      <c r="G102" s="23"/>
       <c r="N102" t="s">
         <v>91</v>
       </c>
-      <c r="O102" s="15"/>
+      <c r="O102" s="23"/>
     </row>
     <row r="110">
       <c r="A110" s="11" t="s">
@@ -2775,11 +2794,11 @@
       <c r="A112" s="19" t="str">
         <f>CONCATENATE("M 22 ",O101)</f>
       </c>
-      <c r="B112" s="19"/>
-      <c r="C112" s="19"/>
-      <c r="D112" s="19"/>
-      <c r="E112" s="19"/>
-      <c r="F112" s="19"/>
+      <c r="B112" s="22"/>
+      <c r="C112" s="22"/>
+      <c r="D112" s="22"/>
+      <c r="E112" s="22"/>
+      <c r="F112" s="22"/>
       <c r="G112" s="19" t="str">
         <f>CONCATENATE("M 21 ",G101)</f>
       </c>
@@ -2788,15 +2807,16 @@
       <c r="F114" t="s">
         <v>90</v>
       </c>
-      <c r="G114" s="15"/>
+      <c r="G114" s="23"/>
     </row>
     <row r="115">
       <c r="F115" t="s">
         <v>91</v>
       </c>
-      <c r="G115" s="15"/>
+      <c r="G115" s="23"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="25">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="I1:O1"/>
@@ -3062,6 +3082,7 @@
       <c r="E35" s="12"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>
@@ -3294,6 +3315,7 @@
       <c r="E35" s="12"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>

--- a/playoffs-example-medium-seeded.xlsx
+++ b/playoffs-example-medium-seeded.xlsx
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName localSheetId="5" name="_xlnm.Print_Area">'Names to Print A'!$A$1:$B$12</definedName>
     <definedName localSheetId="6" name="_xlnm.Print_Area">'Names to Print B'!$A$1:$B$12</definedName>
-    <definedName localSheetId="2" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$O$122</definedName>
+    <definedName localSheetId="2" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$P$122</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
 </workbook>
@@ -1301,7 +1301,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="18" t="str">
-        <f>data!D3</f>
+        <f>'data'!D3</f>
       </c>
     </row>
     <row r="2" ht="270" customHeight="true">
@@ -1309,7 +1309,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="18" t="str">
-        <f>data!D7</f>
+        <f>'data'!D7</f>
       </c>
     </row>
     <row r="3" ht="270" customHeight="true">
@@ -1317,7 +1317,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="18" t="str">
-        <f>data!D8</f>
+        <f>'data'!D8</f>
       </c>
     </row>
     <row r="4" ht="270" customHeight="true">
@@ -1325,7 +1325,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="18" t="str">
-        <f>data!D9</f>
+        <f>'data'!D9</f>
       </c>
     </row>
     <row r="5" ht="270" customHeight="true">
@@ -1333,7 +1333,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="18" t="str">
-        <f>data!D10</f>
+        <f>'data'!D10</f>
       </c>
     </row>
     <row r="6" ht="270" customHeight="true">
@@ -1341,7 +1341,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="18" t="str">
-        <f>data!D11</f>
+        <f>'data'!D11</f>
       </c>
     </row>
     <row r="7" ht="270" customHeight="true">
@@ -1349,7 +1349,7 @@
         <v>9</v>
       </c>
       <c r="B7" s="18" t="str">
-        <f>data!D12</f>
+        <f>'data'!D12</f>
       </c>
     </row>
     <row r="8" ht="270" customHeight="true">
@@ -1357,7 +1357,7 @@
         <v>10</v>
       </c>
       <c r="B8" s="18" t="str">
-        <f>data!D13</f>
+        <f>'data'!D13</f>
       </c>
     </row>
     <row r="9" ht="270" customHeight="true">
@@ -1365,7 +1365,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="18" t="str">
-        <f>data!D6</f>
+        <f>'data'!D6</f>
       </c>
     </row>
     <row r="10" ht="270" customHeight="true">
@@ -1373,7 +1373,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="18" t="str">
-        <f>data!D14</f>
+        <f>'data'!D14</f>
       </c>
     </row>
     <row r="11" ht="270" customHeight="true">
@@ -1381,7 +1381,7 @@
         <v>12</v>
       </c>
       <c r="B11" s="18" t="str">
-        <f>data!D15</f>
+        <f>'data'!D15</f>
       </c>
     </row>
     <row r="12" ht="270" customHeight="true">
@@ -1389,7 +1389,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="18" t="str">
-        <f>data!D16</f>
+        <f>'data'!D16</f>
       </c>
     </row>
   </sheetData>
@@ -1419,7 +1419,7 @@
         <v>14</v>
       </c>
       <c r="B1" s="18" t="str">
-        <f>data!D17</f>
+        <f>'data'!D17</f>
       </c>
     </row>
     <row r="2" ht="270" customHeight="true">
@@ -1427,7 +1427,7 @@
         <v>15</v>
       </c>
       <c r="B2" s="18" t="str">
-        <f>data!D18</f>
+        <f>'data'!D18</f>
       </c>
     </row>
     <row r="3" ht="270" customHeight="true">
@@ -1435,7 +1435,7 @@
         <v>16</v>
       </c>
       <c r="B3" s="18" t="str">
-        <f>data!D19</f>
+        <f>'data'!D19</f>
       </c>
     </row>
     <row r="4" ht="270" customHeight="true">
@@ -1443,7 +1443,7 @@
         <v>17</v>
       </c>
       <c r="B4" s="18" t="str">
-        <f>data!D20</f>
+        <f>'data'!D20</f>
       </c>
     </row>
     <row r="5" ht="270" customHeight="true">
@@ -1451,7 +1451,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="18" t="str">
-        <f>data!D4</f>
+        <f>'data'!D4</f>
       </c>
     </row>
     <row r="6" ht="270" customHeight="true">
@@ -1459,7 +1459,7 @@
         <v>18</v>
       </c>
       <c r="B6" s="18" t="str">
-        <f>data!D21</f>
+        <f>'data'!D21</f>
       </c>
     </row>
     <row r="7" ht="270" customHeight="true">
@@ -1467,7 +1467,7 @@
         <v>19</v>
       </c>
       <c r="B7" s="18" t="str">
-        <f>data!D22</f>
+        <f>'data'!D22</f>
       </c>
     </row>
     <row r="8" ht="270" customHeight="true">
@@ -1475,7 +1475,7 @@
         <v>20</v>
       </c>
       <c r="B8" s="18" t="str">
-        <f>data!D23</f>
+        <f>'data'!D23</f>
       </c>
     </row>
     <row r="9" ht="270" customHeight="true">
@@ -1483,7 +1483,7 @@
         <v>21</v>
       </c>
       <c r="B9" s="18" t="str">
-        <f>data!D24</f>
+        <f>'data'!D24</f>
       </c>
     </row>
     <row r="10" ht="270" customHeight="true">
@@ -1491,7 +1491,7 @@
         <v>22</v>
       </c>
       <c r="B10" s="18" t="str">
-        <f>data!D25</f>
+        <f>'data'!D25</f>
       </c>
     </row>
     <row r="11" ht="270" customHeight="true">
@@ -1499,7 +1499,7 @@
         <v>23</v>
       </c>
       <c r="B11" s="18" t="str">
-        <f>data!D26</f>
+        <f>'data'!D26</f>
       </c>
     </row>
     <row r="12" ht="270" customHeight="true">
@@ -1507,7 +1507,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="18" t="str">
-        <f>data!D5</f>
+        <f>'data'!D5</f>
       </c>
     </row>
   </sheetData>
@@ -1809,19 +1809,14 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="30"/>
-    <col customWidth="true" max="3" min="2" width="5"/>
-    <col customWidth="true" max="4" min="4" width="3"/>
-    <col customWidth="true" max="6" min="5" width="5"/>
+    <col customWidth="true" max="6" min="2" width="5"/>
     <col customWidth="true" max="7" min="7" width="30"/>
     <col customWidth="true" max="8" min="8" width="5"/>
     <col customWidth="true" max="9" min="9" width="30"/>
-    <col customWidth="true" max="11" min="10" width="5"/>
-    <col customWidth="true" max="12" min="12" width="3"/>
-    <col customWidth="true" max="14" min="13" width="5"/>
+    <col customWidth="true" max="14" min="10" width="5"/>
     <col customWidth="true" max="15" min="15" width="30"/>
-    <col customWidth="true" max="18" min="16" width="5"/>
-    <col customWidth="true" max="19" min="19" width="30"/>
-    <col customWidth="true" max="20" min="20" width="2"/>
+    <col customWidth="true" max="16" min="16" width="5"/>
+    <col customWidth="true" max="20" min="17" width="10.83"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/playoffs-example-medium-seeded.xlsx
+++ b/playoffs-example-medium-seeded.xlsx
@@ -16,6 +16,8 @@
     <sheet name="Names to Print B" sheetId="11" r:id="rId14"/>
   </sheets>
   <definedNames>
+    <definedName localSheetId="3" name="_xlnm.Print_Area">'Tree 1'!$A$1:$K$35</definedName>
+    <definedName localSheetId="4" name="_xlnm.Print_Area">'Tree 2'!$A$1:$K$35</definedName>
     <definedName localSheetId="5" name="_xlnm.Print_Area">'Names to Print A'!$A$1:$B$12</definedName>
     <definedName localSheetId="6" name="_xlnm.Print_Area">'Names to Print B'!$A$1:$B$12</definedName>
     <definedName localSheetId="2" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$P$122</definedName>
@@ -2852,12 +2854,17 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="25"/>
-    <col customWidth="true" max="2" min="2" width="10"/>
-    <col customWidth="true" max="26" min="3" width="3.5"/>
+    <col customWidth="true" max="2" min="2" width="4"/>
+    <col customWidth="true" max="3" min="3" width="28"/>
+    <col customWidth="true" max="26" min="4" width="3.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2874,11 +2881,6 @@
       <c r="I1" s="11"/>
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
     </row>
     <row r="6">
       <c r="E6" s="16" t="s">
@@ -3079,18 +3081,25 @@
   </sheetData>
   <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
+  <printOptions horizontalCentered="true" verticalCentered="true"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="25"/>
-    <col customWidth="true" max="2" min="2" width="10"/>
-    <col customWidth="true" max="26" min="3" width="3.5"/>
+    <col customWidth="true" max="2" min="2" width="4"/>
+    <col customWidth="true" max="3" min="3" width="28"/>
+    <col customWidth="true" max="26" min="4" width="3.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3107,11 +3116,6 @@
       <c r="I1" s="11"/>
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
     </row>
     <row r="6">
       <c r="E6" s="16" t="s">
@@ -3312,7 +3316,9 @@
   </sheetData>
   <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
+  <printOptions horizontalCentered="true" verticalCentered="true"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/playoffs-example-medium-seeded.xlsx
+++ b/playoffs-example-medium-seeded.xlsx
@@ -610,7 +610,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
@@ -2883,6 +2883,8 @@
       <c r="K1" s="11"/>
     </row>
     <row r="6">
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
       <c r="E6" s="16" t="s">
         <v>18</v>
       </c>
@@ -2932,6 +2934,8 @@
       <c r="K13" s="12"/>
     </row>
     <row r="14">
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
         <v>36</v>
       </c>
@@ -2985,6 +2989,8 @@
       <c r="K21" s="12"/>
     </row>
     <row r="22">
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
         <v>42</v>
       </c>
@@ -3040,6 +3046,8 @@
       <c r="I29" s="12"/>
     </row>
     <row r="30">
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
         <v>48</v>
       </c>
@@ -3118,6 +3126,8 @@
       <c r="K1" s="11"/>
     </row>
     <row r="6">
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
       <c r="E6" s="16" t="s">
         <v>57</v>
       </c>
@@ -3167,6 +3177,8 @@
       <c r="K13" s="12"/>
     </row>
     <row r="14">
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
         <v>66</v>
       </c>
@@ -3220,6 +3232,8 @@
       <c r="K21" s="12"/>
     </row>
     <row r="22">
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
         <v>71</v>
       </c>
@@ -3275,6 +3289,8 @@
       <c r="I29" s="12"/>
     </row>
     <row r="30">
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
         <v>80</v>
       </c>

--- a/playoffs-example-medium-seeded.xlsx
+++ b/playoffs-example-medium-seeded.xlsx
@@ -1356,10 +1356,10 @@
     </row>
     <row r="8" ht="270" customHeight="true">
       <c r="A8" s="17">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="B8" s="18" t="str">
-        <f>'data'!D13</f>
+        <f>'data'!D26</f>
       </c>
     </row>
     <row r="9" ht="270" customHeight="true">
@@ -1498,10 +1498,10 @@
     </row>
     <row r="11" ht="270" customHeight="true">
       <c r="A11" s="17">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B11" s="18" t="str">
-        <f>'data'!D26</f>
+        <f>'data'!D13</f>
       </c>
     </row>
     <row r="12" ht="270" customHeight="true">
@@ -2059,7 +2059,7 @@
       <c r="E20" s="22"/>
       <c r="F20" s="22"/>
       <c r="G20" s="19" t="str">
-        <f>'data'!$B$13</f>
+        <f>'data'!$B$26</f>
       </c>
       <c r="I20" s="19" t="str">
         <f>'data'!$B$24</f>
@@ -2154,7 +2154,7 @@
       <c r="M28" s="22"/>
       <c r="N28" s="22"/>
       <c r="O28" s="19" t="str">
-        <f>'data'!$B$26</f>
+        <f>'data'!$B$13</f>
       </c>
     </row>
     <row r="30">
@@ -3009,7 +3009,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -3310,7 +3310,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="G33" s="12"/>
     </row>

--- a/playoffs-example-medium-seeded.xlsx
+++ b/playoffs-example-medium-seeded.xlsx
@@ -1348,18 +1348,18 @@
     </row>
     <row r="7" ht="270" customHeight="true">
       <c r="A7" s="17">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B7" s="18" t="str">
-        <f>'data'!D12</f>
+        <f>'data'!D21</f>
       </c>
     </row>
     <row r="8" ht="270" customHeight="true">
       <c r="A8" s="17">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B8" s="18" t="str">
-        <f>'data'!D26</f>
+        <f>'data'!D13</f>
       </c>
     </row>
     <row r="9" ht="270" customHeight="true">
@@ -1458,10 +1458,10 @@
     </row>
     <row r="6" ht="270" customHeight="true">
       <c r="A6" s="17">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B6" s="18" t="str">
-        <f>'data'!D21</f>
+        <f>'data'!D12</f>
       </c>
     </row>
     <row r="7" ht="270" customHeight="true">
@@ -1498,10 +1498,10 @@
     </row>
     <row r="11" ht="270" customHeight="true">
       <c r="A11" s="17">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="B11" s="18" t="str">
-        <f>'data'!D13</f>
+        <f>'data'!D26</f>
       </c>
     </row>
     <row r="12" ht="270" customHeight="true">
@@ -1978,7 +1978,7 @@
         <f>'data'!$B$10</f>
       </c>
       <c r="I12" s="19" t="str">
-        <f>'data'!$B$21</f>
+        <f>'data'!$B$12</f>
       </c>
       <c r="J12" s="22"/>
       <c r="K12" s="22"/>
@@ -2059,7 +2059,7 @@
       <c r="E20" s="22"/>
       <c r="F20" s="22"/>
       <c r="G20" s="19" t="str">
-        <f>'data'!$B$26</f>
+        <f>'data'!$B$13</f>
       </c>
       <c r="I20" s="19" t="str">
         <f>'data'!$B$24</f>
@@ -2154,7 +2154,7 @@
       <c r="M28" s="22"/>
       <c r="N28" s="22"/>
       <c r="O28" s="19" t="str">
-        <f>'data'!$B$13</f>
+        <f>'data'!$B$26</f>
       </c>
     </row>
     <row r="30">
@@ -2395,7 +2395,7 @@
       <c r="E57" s="22"/>
       <c r="F57" s="22"/>
       <c r="G57" s="19" t="str">
-        <f>'data'!$B$12</f>
+        <f>'data'!$B$21</f>
       </c>
       <c r="I57" s="19" t="str">
         <f>CONCATENATE("M 7 ",O22)</f>
@@ -2992,7 +2992,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="K22" s="12"/>
     </row>
@@ -3009,7 +3009,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -3217,7 +3217,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -3310,7 +3310,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="G33" s="12"/>
     </row>

--- a/playoffs-example-medium-seeded.xlsx
+++ b/playoffs-example-medium-seeded.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="146">
   <si>
     <t>Number of pools</t>
   </si>
@@ -74,6 +74,9 @@
     <t>Display Name</t>
   </si>
   <si>
+    <t>Player Number</t>
+  </si>
+  <si>
     <t>Metadata</t>
   </si>
   <si>
@@ -86,6 +89,9 @@
     <t>LANNISTER</t>
   </si>
   <si>
+    <t>K1</t>
+  </si>
+  <si>
     <t>Daenerys Targaryen</t>
   </si>
   <si>
@@ -95,6 +101,9 @@
     <t>TARGARYEN</t>
   </si>
   <si>
+    <t>K2</t>
+  </si>
+  <si>
     <t>Eddard Stark</t>
   </si>
   <si>
@@ -104,6 +113,9 @@
     <t>STARK</t>
   </si>
   <si>
+    <t>K3</t>
+  </si>
+  <si>
     <t>Frodo Baggins</t>
   </si>
   <si>
@@ -113,6 +125,9 @@
     <t>BAGGINS</t>
   </si>
   <si>
+    <t>K4</t>
+  </si>
+  <si>
     <t>Gandalf The Grey</t>
   </si>
   <si>
@@ -122,6 +137,9 @@
     <t>GANDALF</t>
   </si>
   <si>
+    <t>K5</t>
+  </si>
+  <si>
     <t>Hermione Granger</t>
   </si>
   <si>
@@ -131,6 +149,9 @@
     <t>GRANGER</t>
   </si>
   <si>
+    <t>K6</t>
+  </si>
+  <si>
     <t>Inigo Montoya</t>
   </si>
   <si>
@@ -140,6 +161,9 @@
     <t>MONTOYA</t>
   </si>
   <si>
+    <t>K7</t>
+  </si>
+  <si>
     <t>Jon Snow</t>
   </si>
   <si>
@@ -149,6 +173,9 @@
     <t>SNOW</t>
   </si>
   <si>
+    <t>K8</t>
+  </si>
+  <si>
     <t>Katniss Everdeen</t>
   </si>
   <si>
@@ -158,15 +185,24 @@
     <t>EVERDEEN</t>
   </si>
   <si>
+    <t>K9</t>
+  </si>
+  <si>
     <t>Team Mu</t>
   </si>
   <si>
+    <t>K10</t>
+  </si>
+  <si>
     <t>Legolas Greenleaf</t>
   </si>
   <si>
     <t>GREENLEAF</t>
   </si>
   <si>
+    <t>K11</t>
+  </si>
+  <si>
     <t>Moby Dick</t>
   </si>
   <si>
@@ -176,6 +212,9 @@
     <t>DICK</t>
   </si>
   <si>
+    <t>K12</t>
+  </si>
+  <si>
     <t>Neville Longbottom</t>
   </si>
   <si>
@@ -185,6 +224,9 @@
     <t>LONGBOTTOM</t>
   </si>
   <si>
+    <t>K13</t>
+  </si>
+  <si>
     <t>Othello</t>
   </si>
   <si>
@@ -194,6 +236,9 @@
     <t>OTHELLO</t>
   </si>
   <si>
+    <t>K14</t>
+  </si>
+  <si>
     <t>Petyr Baelish</t>
   </si>
   <si>
@@ -203,6 +248,9 @@
     <t>BAELISH</t>
   </si>
   <si>
+    <t>K15</t>
+  </si>
+  <si>
     <t>Quirinus Quirrell</t>
   </si>
   <si>
@@ -212,6 +260,9 @@
     <t>QUIRRELL</t>
   </si>
   <si>
+    <t>K16</t>
+  </si>
+  <si>
     <t>Ron Weasley</t>
   </si>
   <si>
@@ -221,6 +272,9 @@
     <t>WEASLEY</t>
   </si>
   <si>
+    <t>K17</t>
+  </si>
+  <si>
     <t>Samwise Gamgee</t>
   </si>
   <si>
@@ -230,12 +284,18 @@
     <t>GAMGEE</t>
   </si>
   <si>
+    <t>K18</t>
+  </si>
+  <si>
     <t>Tyrion Lannister</t>
   </si>
   <si>
     <t>Team Upsilon</t>
   </si>
   <si>
+    <t>K19</t>
+  </si>
+  <si>
     <t>Ulysses</t>
   </si>
   <si>
@@ -245,6 +305,9 @@
     <t>ULYSSES</t>
   </si>
   <si>
+    <t>K20</t>
+  </si>
+  <si>
     <t>Voldemort</t>
   </si>
   <si>
@@ -254,6 +317,9 @@
     <t>VOLDEMORT</t>
   </si>
   <si>
+    <t>K21</t>
+  </si>
+  <si>
     <t>Willy Wonka</t>
   </si>
   <si>
@@ -263,6 +329,9 @@
     <t>WONKA</t>
   </si>
   <si>
+    <t>K22</t>
+  </si>
+  <si>
     <t>Xaro Xhoan Daxos</t>
   </si>
   <si>
@@ -272,6 +341,9 @@
     <t>DAXOS</t>
   </si>
   <si>
+    <t>K23</t>
+  </si>
+  <si>
     <t>Ygritte</t>
   </si>
   <si>
@@ -279,6 +351,9 @@
   </si>
   <si>
     <t>YGRITTE</t>
+  </si>
+  <si>
+    <t>K24</t>
   </si>
   <si>
     <t>Shiaijo A</t>
@@ -947,19 +1022,25 @@
       <c r="E2" t="s">
         <v>15</v>
       </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3">
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -967,13 +1048,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="5">
@@ -981,13 +1065,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>27</v>
+      </c>
+      <c r="E5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="6">
@@ -995,13 +1082,16 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>31</v>
+      </c>
+      <c r="E6" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="7">
@@ -1009,13 +1099,16 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>35</v>
+      </c>
+      <c r="E7" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="8">
@@ -1023,13 +1116,16 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>39</v>
+      </c>
+      <c r="E8" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="9">
@@ -1037,13 +1133,16 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>43</v>
+      </c>
+      <c r="E9" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="10">
@@ -1051,13 +1150,16 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>39</v>
+        <v>47</v>
+      </c>
+      <c r="E10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="11">
@@ -1065,13 +1167,16 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>51</v>
+      </c>
+      <c r="E11" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="12">
@@ -1079,13 +1184,16 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="D12" t="s">
-        <v>42</v>
+        <v>51</v>
+      </c>
+      <c r="E12" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="13">
@@ -1093,13 +1201,16 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="C13" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="D13" t="s">
-        <v>45</v>
+        <v>56</v>
+      </c>
+      <c r="E13" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="14">
@@ -1107,13 +1218,16 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="D14" t="s">
-        <v>48</v>
+        <v>60</v>
+      </c>
+      <c r="E14" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -1121,13 +1235,16 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C15" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="D15" t="s">
-        <v>51</v>
+        <v>64</v>
+      </c>
+      <c r="E15" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="16">
@@ -1135,13 +1252,16 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D16" t="s">
-        <v>54</v>
+        <v>68</v>
+      </c>
+      <c r="E16" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="17">
@@ -1149,13 +1269,16 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="C17" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="D17" t="s">
-        <v>57</v>
+        <v>72</v>
+      </c>
+      <c r="E17" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -1163,13 +1286,16 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="C18" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="D18" t="s">
-        <v>60</v>
+        <v>76</v>
+      </c>
+      <c r="E18" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="19">
@@ -1177,13 +1303,16 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="C19" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="D19" t="s">
-        <v>63</v>
+        <v>80</v>
+      </c>
+      <c r="E19" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="20">
@@ -1191,13 +1320,16 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="C20" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="D20" t="s">
-        <v>66</v>
+        <v>84</v>
+      </c>
+      <c r="E20" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="21">
@@ -1205,13 +1337,16 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="C21" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="D21" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="E21" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="22">
@@ -1219,13 +1354,16 @@
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="C22" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="D22" t="s">
-        <v>71</v>
+        <v>91</v>
+      </c>
+      <c r="E22" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="23">
@@ -1233,13 +1371,16 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="C23" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="D23" t="s">
-        <v>74</v>
+        <v>95</v>
+      </c>
+      <c r="E23" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="24">
@@ -1247,13 +1388,16 @@
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="C24" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="D24" t="s">
-        <v>77</v>
+        <v>99</v>
+      </c>
+      <c r="E24" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="25">
@@ -1261,13 +1405,16 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="C25" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="D25" t="s">
-        <v>80</v>
+        <v>103</v>
+      </c>
+      <c r="E25" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="26">
@@ -1275,13 +1422,16 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="C26" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="D26" t="s">
-        <v>83</v>
+        <v>107</v>
+      </c>
+      <c r="E26" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -1299,96 +1449,96 @@
   </cols>
   <sheetData>
     <row r="1" ht="270" customHeight="true">
-      <c r="A1" s="17">
-        <v>0</v>
+      <c r="A1" s="17" t="str">
+        <f>'data'!$E$3</f>
       </c>
       <c r="B1" s="18" t="str">
         <f>'data'!D3</f>
       </c>
     </row>
     <row r="2" ht="270" customHeight="true">
-      <c r="A2" s="17">
-        <v>4</v>
+      <c r="A2" s="17" t="str">
+        <f>'data'!$E$7</f>
       </c>
       <c r="B2" s="18" t="str">
         <f>'data'!D7</f>
       </c>
     </row>
     <row r="3" ht="270" customHeight="true">
-      <c r="A3" s="17">
-        <v>5</v>
+      <c r="A3" s="17" t="str">
+        <f>'data'!$E$8</f>
       </c>
       <c r="B3" s="18" t="str">
         <f>'data'!D8</f>
       </c>
     </row>
     <row r="4" ht="270" customHeight="true">
-      <c r="A4" s="17">
-        <v>6</v>
+      <c r="A4" s="17" t="str">
+        <f>'data'!$E$9</f>
       </c>
       <c r="B4" s="18" t="str">
         <f>'data'!D9</f>
       </c>
     </row>
     <row r="5" ht="270" customHeight="true">
-      <c r="A5" s="17">
-        <v>7</v>
+      <c r="A5" s="17" t="str">
+        <f>'data'!$E$10</f>
       </c>
       <c r="B5" s="18" t="str">
         <f>'data'!D10</f>
       </c>
     </row>
     <row r="6" ht="270" customHeight="true">
-      <c r="A6" s="17">
-        <v>8</v>
+      <c r="A6" s="17" t="str">
+        <f>'data'!$E$11</f>
       </c>
       <c r="B6" s="18" t="str">
         <f>'data'!D11</f>
       </c>
     </row>
     <row r="7" ht="270" customHeight="true">
-      <c r="A7" s="17">
-        <v>18</v>
+      <c r="A7" s="17" t="str">
+        <f>'data'!$E$21</f>
       </c>
       <c r="B7" s="18" t="str">
         <f>'data'!D21</f>
       </c>
     </row>
     <row r="8" ht="270" customHeight="true">
-      <c r="A8" s="17">
-        <v>10</v>
+      <c r="A8" s="17" t="str">
+        <f>'data'!$E$13</f>
       </c>
       <c r="B8" s="18" t="str">
         <f>'data'!D13</f>
       </c>
     </row>
     <row r="9" ht="270" customHeight="true">
-      <c r="A9" s="17">
-        <v>3</v>
+      <c r="A9" s="17" t="str">
+        <f>'data'!$E$6</f>
       </c>
       <c r="B9" s="18" t="str">
         <f>'data'!D6</f>
       </c>
     </row>
     <row r="10" ht="270" customHeight="true">
-      <c r="A10" s="17">
-        <v>11</v>
+      <c r="A10" s="17" t="str">
+        <f>'data'!$E$14</f>
       </c>
       <c r="B10" s="18" t="str">
         <f>'data'!D14</f>
       </c>
     </row>
     <row r="11" ht="270" customHeight="true">
-      <c r="A11" s="17">
-        <v>12</v>
+      <c r="A11" s="17" t="str">
+        <f>'data'!$E$15</f>
       </c>
       <c r="B11" s="18" t="str">
         <f>'data'!D15</f>
       </c>
     </row>
     <row r="12" ht="270" customHeight="true">
-      <c r="A12" s="17">
-        <v>13</v>
+      <c r="A12" s="17" t="str">
+        <f>'data'!$E$16</f>
       </c>
       <c r="B12" s="18" t="str">
         <f>'data'!D16</f>
@@ -1417,96 +1567,96 @@
   </cols>
   <sheetData>
     <row r="1" ht="270" customHeight="true">
-      <c r="A1" s="17">
-        <v>14</v>
+      <c r="A1" s="17" t="str">
+        <f>'data'!$E$17</f>
       </c>
       <c r="B1" s="18" t="str">
         <f>'data'!D17</f>
       </c>
     </row>
     <row r="2" ht="270" customHeight="true">
-      <c r="A2" s="17">
-        <v>15</v>
+      <c r="A2" s="17" t="str">
+        <f>'data'!$E$18</f>
       </c>
       <c r="B2" s="18" t="str">
         <f>'data'!D18</f>
       </c>
     </row>
     <row r="3" ht="270" customHeight="true">
-      <c r="A3" s="17">
-        <v>16</v>
+      <c r="A3" s="17" t="str">
+        <f>'data'!$E$19</f>
       </c>
       <c r="B3" s="18" t="str">
         <f>'data'!D19</f>
       </c>
     </row>
     <row r="4" ht="270" customHeight="true">
-      <c r="A4" s="17">
-        <v>17</v>
+      <c r="A4" s="17" t="str">
+        <f>'data'!$E$20</f>
       </c>
       <c r="B4" s="18" t="str">
         <f>'data'!D20</f>
       </c>
     </row>
     <row r="5" ht="270" customHeight="true">
-      <c r="A5" s="17">
-        <v>1</v>
+      <c r="A5" s="17" t="str">
+        <f>'data'!$E$4</f>
       </c>
       <c r="B5" s="18" t="str">
         <f>'data'!D4</f>
       </c>
     </row>
     <row r="6" ht="270" customHeight="true">
-      <c r="A6" s="17">
-        <v>9</v>
+      <c r="A6" s="17" t="str">
+        <f>'data'!$E$12</f>
       </c>
       <c r="B6" s="18" t="str">
         <f>'data'!D12</f>
       </c>
     </row>
     <row r="7" ht="270" customHeight="true">
-      <c r="A7" s="17">
-        <v>19</v>
+      <c r="A7" s="17" t="str">
+        <f>'data'!$E$22</f>
       </c>
       <c r="B7" s="18" t="str">
         <f>'data'!D22</f>
       </c>
     </row>
     <row r="8" ht="270" customHeight="true">
-      <c r="A8" s="17">
-        <v>20</v>
+      <c r="A8" s="17" t="str">
+        <f>'data'!$E$23</f>
       </c>
       <c r="B8" s="18" t="str">
         <f>'data'!D23</f>
       </c>
     </row>
     <row r="9" ht="270" customHeight="true">
-      <c r="A9" s="17">
-        <v>21</v>
+      <c r="A9" s="17" t="str">
+        <f>'data'!$E$24</f>
       </c>
       <c r="B9" s="18" t="str">
         <f>'data'!D24</f>
       </c>
     </row>
     <row r="10" ht="270" customHeight="true">
-      <c r="A10" s="17">
-        <v>22</v>
+      <c r="A10" s="17" t="str">
+        <f>'data'!$E$25</f>
       </c>
       <c r="B10" s="18" t="str">
         <f>'data'!D25</f>
       </c>
     </row>
     <row r="11" ht="270" customHeight="true">
-      <c r="A11" s="17">
-        <v>23</v>
+      <c r="A11" s="17" t="str">
+        <f>'data'!$E$26</f>
       </c>
       <c r="B11" s="18" t="str">
         <f>'data'!D26</f>
       </c>
     </row>
     <row r="12" ht="270" customHeight="true">
-      <c r="A12" s="17">
-        <v>2</v>
+      <c r="A12" s="17" t="str">
+        <f>'data'!$E$5</f>
       </c>
       <c r="B12" s="18" t="str">
         <f>'data'!D5</f>
@@ -1726,7 +1876,7 @@
     </row>
     <row r="13">
       <c r="E13" s="11" t="s">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="F13" s="11"/>
       <c r="G13" s="11"/>
@@ -1737,7 +1887,7 @@
         <v>2</v>
       </c>
       <c r="E14" s="25" t="s">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="F14" s="25"/>
       <c r="G14" s="25"/>
@@ -1747,7 +1897,7 @@
     </row>
     <row r="15">
       <c r="E15" s="25" t="s">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="F15" s="25"/>
       <c r="G15" s="25"/>
@@ -1757,7 +1907,7 @@
     </row>
     <row r="16">
       <c r="E16" s="25" t="s">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="F16" s="25"/>
       <c r="G16" s="25"/>
@@ -1767,7 +1917,7 @@
     </row>
     <row r="17">
       <c r="E17" s="25" t="s">
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="F17" s="25"/>
       <c r="G17" s="25"/>
@@ -1777,7 +1927,7 @@
     </row>
     <row r="18">
       <c r="E18" s="11" t="s">
-        <v>119</v>
+        <v>144</v>
       </c>
       <c r="F18" s="11"/>
       <c r="G18" s="11"/>
@@ -1787,7 +1937,7 @@
     </row>
     <row r="19">
       <c r="E19" s="11" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="F19" s="11"/>
       <c r="G19" s="11"/>
@@ -1823,7 +1973,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="11" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -1832,7 +1982,7 @@
       <c r="F1" s="11"/>
       <c r="G1" s="11"/>
       <c r="I1" s="11" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
@@ -1843,7 +1993,7 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
@@ -1852,7 +2002,7 @@
       <c r="F2" s="11"/>
       <c r="G2" s="11"/>
       <c r="I2" s="11" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
@@ -1863,22 +2013,22 @@
     </row>
     <row r="3">
       <c r="A3" s="21" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="L3" s="19" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="O3" s="20" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4">
@@ -1907,27 +2057,27 @@
     </row>
     <row r="6">
       <c r="F6" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="G6" s="23"/>
       <c r="N6" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="O6" s="23"/>
     </row>
     <row r="7">
       <c r="F7" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="G7" s="23"/>
       <c r="N7" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="O7" s="23"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -1936,7 +2086,7 @@
       <c r="F10" s="11"/>
       <c r="G10" s="11"/>
       <c r="I10" s="11" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="J10" s="11"/>
       <c r="K10" s="11"/>
@@ -1947,22 +2097,22 @@
     </row>
     <row r="11">
       <c r="A11" s="21" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="I11" s="21" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="L11" s="19" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="O11" s="20" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12">
@@ -1991,27 +2141,27 @@
     </row>
     <row r="14">
       <c r="F14" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="G14" s="23"/>
       <c r="N14" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="O14" s="23"/>
     </row>
     <row r="15">
       <c r="F15" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="G15" s="23"/>
       <c r="N15" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="O15" s="23"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -2020,7 +2170,7 @@
       <c r="F18" s="11"/>
       <c r="G18" s="11"/>
       <c r="I18" s="11" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
@@ -2031,22 +2181,22 @@
     </row>
     <row r="19">
       <c r="A19" s="21" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="G19" s="20" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="I19" s="21" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="L19" s="19" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="O19" s="20" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20">
@@ -2075,27 +2225,27 @@
     </row>
     <row r="22">
       <c r="F22" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="G22" s="23"/>
       <c r="N22" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="O22" s="23"/>
     </row>
     <row r="23">
       <c r="F23" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="G23" s="23"/>
       <c r="N23" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="O23" s="23"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -2104,7 +2254,7 @@
       <c r="F26" s="11"/>
       <c r="G26" s="11"/>
       <c r="I26" s="11" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="J26" s="11"/>
       <c r="K26" s="11"/>
@@ -2115,22 +2265,22 @@
     </row>
     <row r="27">
       <c r="A27" s="21" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="G27" s="20" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="I27" s="21" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="L27" s="19" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="O27" s="20" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
     </row>
     <row r="28">
@@ -2159,27 +2309,27 @@
     </row>
     <row r="30">
       <c r="F30" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="G30" s="23"/>
       <c r="N30" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="O30" s="23"/>
     </row>
     <row r="31">
       <c r="F31" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="G31" s="23"/>
       <c r="N31" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="O31" s="23"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -2188,7 +2338,7 @@
       <c r="F39" s="11"/>
       <c r="G39" s="11"/>
       <c r="I39" s="11" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="J39" s="11"/>
       <c r="K39" s="11"/>
@@ -2199,22 +2349,22 @@
     </row>
     <row r="40">
       <c r="A40" s="21" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="D40" s="19" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="G40" s="20" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="I40" s="21" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="L40" s="19" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="O40" s="20" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
     </row>
     <row r="41">
@@ -2243,27 +2393,27 @@
     </row>
     <row r="43">
       <c r="F43" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="G43" s="23"/>
       <c r="N43" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="O43" s="23"/>
     </row>
     <row r="44">
       <c r="F44" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="G44" s="23"/>
       <c r="N44" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="O44" s="23"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="B47" s="11"/>
       <c r="C47" s="11"/>
@@ -2272,7 +2422,7 @@
       <c r="F47" s="11"/>
       <c r="G47" s="11"/>
       <c r="I47" s="11" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="J47" s="11"/>
       <c r="K47" s="11"/>
@@ -2283,22 +2433,22 @@
     </row>
     <row r="48">
       <c r="A48" s="21" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="D48" s="19" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="G48" s="20" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="I48" s="21" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="L48" s="19" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="O48" s="20" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
     </row>
     <row r="49">
@@ -2327,27 +2477,27 @@
     </row>
     <row r="51">
       <c r="F51" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="G51" s="23"/>
       <c r="N51" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="O51" s="23"/>
     </row>
     <row r="52">
       <c r="F52" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="G52" s="23"/>
       <c r="N52" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="O52" s="23"/>
     </row>
     <row r="55">
       <c r="A55" s="11" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="B55" s="11"/>
       <c r="C55" s="11"/>
@@ -2356,7 +2506,7 @@
       <c r="F55" s="11"/>
       <c r="G55" s="11"/>
       <c r="I55" s="11" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="J55" s="11"/>
       <c r="K55" s="11"/>
@@ -2367,22 +2517,22 @@
     </row>
     <row r="56">
       <c r="A56" s="21" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="D56" s="19" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="G56" s="20" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="I56" s="21" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="L56" s="19" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="O56" s="20" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
     </row>
     <row r="57">
@@ -2411,27 +2561,27 @@
     </row>
     <row r="59">
       <c r="F59" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="G59" s="23"/>
       <c r="N59" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="O59" s="23"/>
     </row>
     <row r="60">
       <c r="F60" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="G60" s="23"/>
       <c r="N60" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="O60" s="23"/>
     </row>
     <row r="63">
       <c r="A63" s="11" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="B63" s="11"/>
       <c r="C63" s="11"/>
@@ -2440,7 +2590,7 @@
       <c r="F63" s="11"/>
       <c r="G63" s="11"/>
       <c r="I63" s="11" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="J63" s="11"/>
       <c r="K63" s="11"/>
@@ -2451,22 +2601,22 @@
     </row>
     <row r="64">
       <c r="A64" s="21" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="D64" s="19" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="G64" s="20" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="I64" s="21" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="L64" s="19" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="O64" s="20" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
     </row>
     <row r="65">
@@ -2495,27 +2645,27 @@
     </row>
     <row r="67">
       <c r="F67" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="G67" s="23"/>
       <c r="N67" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="O67" s="23"/>
     </row>
     <row r="68">
       <c r="F68" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="G68" s="23"/>
       <c r="N68" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="O68" s="23"/>
     </row>
     <row r="76">
       <c r="A76" s="11" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="B76" s="11"/>
       <c r="C76" s="11"/>
@@ -2524,7 +2674,7 @@
       <c r="F76" s="11"/>
       <c r="G76" s="11"/>
       <c r="I76" s="11" t="s">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="J76" s="11"/>
       <c r="K76" s="11"/>
@@ -2535,22 +2685,22 @@
     </row>
     <row r="77">
       <c r="A77" s="21" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="D77" s="19" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="G77" s="20" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="I77" s="21" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="L77" s="19" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="O77" s="20" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
     </row>
     <row r="78">
@@ -2579,27 +2729,27 @@
     </row>
     <row r="80">
       <c r="F80" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="G80" s="23"/>
       <c r="N80" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="O80" s="23"/>
     </row>
     <row r="81">
       <c r="F81" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="G81" s="23"/>
       <c r="N81" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="O81" s="23"/>
     </row>
     <row r="84">
       <c r="A84" s="11" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="B84" s="11"/>
       <c r="C84" s="11"/>
@@ -2608,7 +2758,7 @@
       <c r="F84" s="11"/>
       <c r="G84" s="11"/>
       <c r="I84" s="11" t="s">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="J84" s="11"/>
       <c r="K84" s="11"/>
@@ -2619,22 +2769,22 @@
     </row>
     <row r="85">
       <c r="A85" s="21" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="D85" s="19" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="G85" s="20" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="I85" s="21" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="L85" s="19" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="O85" s="20" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
     </row>
     <row r="86">
@@ -2663,27 +2813,27 @@
     </row>
     <row r="88">
       <c r="F88" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="G88" s="23"/>
       <c r="N88" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="O88" s="23"/>
     </row>
     <row r="89">
       <c r="F89" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="G89" s="23"/>
       <c r="N89" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="O89" s="23"/>
     </row>
     <row r="97">
       <c r="A97" s="11" t="s">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="B97" s="11"/>
       <c r="C97" s="11"/>
@@ -2692,7 +2842,7 @@
       <c r="F97" s="11"/>
       <c r="G97" s="11"/>
       <c r="I97" s="11" t="s">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="J97" s="11"/>
       <c r="K97" s="11"/>
@@ -2703,22 +2853,22 @@
     </row>
     <row r="98">
       <c r="A98" s="21" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="D98" s="19" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="G98" s="20" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="I98" s="21" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="L98" s="19" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="O98" s="20" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
     </row>
     <row r="99">
@@ -2747,27 +2897,27 @@
     </row>
     <row r="101">
       <c r="F101" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="G101" s="23"/>
       <c r="N101" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="O101" s="23"/>
     </row>
     <row r="102">
       <c r="F102" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="G102" s="23"/>
       <c r="N102" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="O102" s="23"/>
     </row>
     <row r="110">
       <c r="A110" s="11" t="s">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="B110" s="11"/>
       <c r="C110" s="11"/>
@@ -2778,13 +2928,13 @@
     </row>
     <row r="111">
       <c r="A111" s="21" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="D111" s="19" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="G111" s="20" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
     </row>
     <row r="112">
@@ -2802,13 +2952,13 @@
     </row>
     <row r="114">
       <c r="F114" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="G114" s="23"/>
     </row>
     <row r="115">
       <c r="F115" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="G115" s="23"/>
     </row>
@@ -2886,7 +3036,7 @@
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
       <c r="E6" s="16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
@@ -2900,7 +3050,7 @@
     </row>
     <row r="9">
       <c r="C9" s="16" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G9" s="12"/>
       <c r="H9" s="14"/>
@@ -2917,7 +3067,7 @@
     </row>
     <row r="11">
       <c r="C11" s="16" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="12"/>
@@ -2937,7 +3087,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -2958,7 +3108,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -2974,7 +3124,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -2992,7 +3142,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K22" s="12"/>
     </row>
@@ -3009,7 +3159,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -3028,7 +3178,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -3049,7 +3199,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -3067,7 +3217,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -3081,7 +3231,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>
@@ -3129,7 +3279,7 @@
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
       <c r="E6" s="16" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -3143,7 +3293,7 @@
     </row>
     <row r="9">
       <c r="C9" s="16" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="G9" s="12"/>
       <c r="H9" s="14"/>
@@ -3160,7 +3310,7 @@
     </row>
     <row r="11">
       <c r="C11" s="16" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="12"/>
@@ -3180,7 +3330,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -3201,7 +3351,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -3217,7 +3367,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -3235,7 +3385,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="K22" s="12"/>
     </row>
@@ -3252,7 +3402,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -3271,7 +3421,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -3292,7 +3442,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -3310,7 +3460,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -3324,7 +3474,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>

--- a/playoffs-example-medium-seeded.xlsx
+++ b/playoffs-example-medium-seeded.xlsx
@@ -62,7 +62,7 @@
     <t/>
   </si>
   <si>
-    <t>Number</t>
+    <t>Draw order</t>
   </si>
   <si>
     <t>Player Name</t>
@@ -689,7 +689,7 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
@@ -1028,7 +1028,7 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
@@ -1045,7 +1045,7 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
@@ -1062,7 +1062,7 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
@@ -1079,7 +1079,7 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
         <v>29</v>
@@ -1096,7 +1096,7 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>33</v>
@@ -1113,7 +1113,7 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
         <v>37</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
         <v>41</v>
@@ -1147,7 +1147,7 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
         <v>45</v>
@@ -1164,7 +1164,7 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
         <v>49</v>
@@ -1181,7 +1181,7 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s">
         <v>49</v>
@@ -1198,7 +1198,7 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
         <v>55</v>
@@ -1215,7 +1215,7 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
         <v>58</v>
@@ -1232,7 +1232,7 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
         <v>62</v>
@@ -1249,7 +1249,7 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16" t="s">
         <v>66</v>
@@ -1266,7 +1266,7 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B17" t="s">
         <v>70</v>
@@ -1283,7 +1283,7 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B18" t="s">
         <v>74</v>
@@ -1300,7 +1300,7 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
         <v>78</v>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B20" t="s">
         <v>82</v>
@@ -1334,7 +1334,7 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B21" t="s">
         <v>86</v>
@@ -1351,7 +1351,7 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B22" t="s">
         <v>89</v>
@@ -1368,7 +1368,7 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B23" t="s">
         <v>93</v>
@@ -1385,7 +1385,7 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B24" t="s">
         <v>97</v>
@@ -1402,7 +1402,7 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B25" t="s">
         <v>101</v>
@@ -1419,7 +1419,7 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B26" t="s">
         <v>105</v>

--- a/playoffs-example-medium-seeded.xlsx
+++ b/playoffs-example-medium-seeded.xlsx
@@ -1348,10 +1348,10 @@
     </row>
     <row r="7" ht="270" customHeight="true">
       <c r="A7" s="17">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B7" s="18" t="str">
-        <f>'data'!D21</f>
+        <f>'data'!D17</f>
       </c>
     </row>
     <row r="8" ht="270" customHeight="true">
@@ -1418,10 +1418,10 @@
   <sheetData>
     <row r="1" ht="270" customHeight="true">
       <c r="A1" s="17">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B1" s="18" t="str">
-        <f>'data'!D17</f>
+        <f>'data'!D12</f>
       </c>
     </row>
     <row r="2" ht="270" customHeight="true">
@@ -1458,10 +1458,10 @@
     </row>
     <row r="6" ht="270" customHeight="true">
       <c r="A6" s="17">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B6" s="18" t="str">
-        <f>'data'!D12</f>
+        <f>'data'!D21</f>
       </c>
     </row>
     <row r="7" ht="270" customHeight="true">
@@ -1978,7 +1978,7 @@
         <f>'data'!$B$10</f>
       </c>
       <c r="I12" s="19" t="str">
-        <f>'data'!$B$12</f>
+        <f>'data'!$B$21</f>
       </c>
       <c r="J12" s="22"/>
       <c r="K12" s="22"/>
@@ -2238,7 +2238,7 @@
       <c r="M41" s="22"/>
       <c r="N41" s="22"/>
       <c r="O41" s="19" t="str">
-        <f>'data'!$B$17</f>
+        <f>'data'!$B$12</f>
       </c>
     </row>
     <row r="43">
@@ -2395,7 +2395,7 @@
       <c r="E57" s="22"/>
       <c r="F57" s="22"/>
       <c r="G57" s="19" t="str">
-        <f>'data'!$B$21</f>
+        <f>'data'!$B$17</f>
       </c>
       <c r="I57" s="19" t="str">
         <f>CONCATENATE("M 7 ",O22)</f>
@@ -2992,7 +2992,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="K22" s="12"/>
     </row>
@@ -3129,7 +3129,7 @@
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
       <c r="E6" s="16" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">
@@ -3217,7 +3217,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>

--- a/playoffs-example-medium-seeded.xlsx
+++ b/playoffs-example-medium-seeded.xlsx
@@ -692,7 +692,7 @@
       <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
@@ -1444,8 +1444,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="30"/>
-    <col customWidth="true" max="2" min="2" width="160"/>
+    <col customWidth="true" max="1" min="1" width="40"/>
+    <col customWidth="true" max="2" min="2" width="140"/>
   </cols>
   <sheetData>
     <row r="1" ht="270" customHeight="true">
@@ -1562,8 +1562,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="30"/>
-    <col customWidth="true" max="2" min="2" width="160"/>
+    <col customWidth="true" max="1" min="1" width="40"/>
+    <col customWidth="true" max="2" min="2" width="140"/>
   </cols>
   <sheetData>
     <row r="1" ht="270" customHeight="true">

--- a/playoffs-example-medium-seeded.xlsx
+++ b/playoffs-example-medium-seeded.xlsx
@@ -62,7 +62,7 @@
     <t/>
   </si>
   <si>
-    <t>Draw order</t>
+    <t>Entry order</t>
   </si>
   <si>
     <t>Player Name</t>

--- a/playoffs-example-medium-seeded.xlsx
+++ b/playoffs-example-medium-seeded.xlsx
@@ -92,6 +92,177 @@
     <t>K1</t>
   </si>
   <si>
+    <t>Gandalf The Grey</t>
+  </si>
+  <si>
+    <t>Team Eta</t>
+  </si>
+  <si>
+    <t>GANDALF</t>
+  </si>
+  <si>
+    <t>K2</t>
+  </si>
+  <si>
+    <t>Hermione Granger</t>
+  </si>
+  <si>
+    <t>Team Theta</t>
+  </si>
+  <si>
+    <t>GRANGER</t>
+  </si>
+  <si>
+    <t>K3</t>
+  </si>
+  <si>
+    <t>Inigo Montoya</t>
+  </si>
+  <si>
+    <t>Team Iota</t>
+  </si>
+  <si>
+    <t>MONTOYA</t>
+  </si>
+  <si>
+    <t>K4</t>
+  </si>
+  <si>
+    <t>Jon Snow</t>
+  </si>
+  <si>
+    <t>Team Kappa</t>
+  </si>
+  <si>
+    <t>SNOW</t>
+  </si>
+  <si>
+    <t>K5</t>
+  </si>
+  <si>
+    <t>Katniss Everdeen</t>
+  </si>
+  <si>
+    <t>Team Lambda</t>
+  </si>
+  <si>
+    <t>EVERDEEN</t>
+  </si>
+  <si>
+    <t>K6</t>
+  </si>
+  <si>
+    <t>Petyr Baelish</t>
+  </si>
+  <si>
+    <t>Team Pi</t>
+  </si>
+  <si>
+    <t>BAELISH</t>
+  </si>
+  <si>
+    <t>K7</t>
+  </si>
+  <si>
+    <t>Legolas Greenleaf</t>
+  </si>
+  <si>
+    <t>Team Mu</t>
+  </si>
+  <si>
+    <t>GREENLEAF</t>
+  </si>
+  <si>
+    <t>K8</t>
+  </si>
+  <si>
+    <t>Frodo Baggins</t>
+  </si>
+  <si>
+    <t>Team Zeta</t>
+  </si>
+  <si>
+    <t>BAGGINS</t>
+  </si>
+  <si>
+    <t>K9</t>
+  </si>
+  <si>
+    <t>Moby Dick</t>
+  </si>
+  <si>
+    <t>Team Nu</t>
+  </si>
+  <si>
+    <t>DICK</t>
+  </si>
+  <si>
+    <t>K10</t>
+  </si>
+  <si>
+    <t>Neville Longbottom</t>
+  </si>
+  <si>
+    <t>Team Xi</t>
+  </si>
+  <si>
+    <t>LONGBOTTOM</t>
+  </si>
+  <si>
+    <t>K11</t>
+  </si>
+  <si>
+    <t>Othello</t>
+  </si>
+  <si>
+    <t>Team Omicron</t>
+  </si>
+  <si>
+    <t>OTHELLO</t>
+  </si>
+  <si>
+    <t>K12</t>
+  </si>
+  <si>
+    <t>K13</t>
+  </si>
+  <si>
+    <t>Quirinus Quirrell</t>
+  </si>
+  <si>
+    <t>Team Rho</t>
+  </si>
+  <si>
+    <t>QUIRRELL</t>
+  </si>
+  <si>
+    <t>K14</t>
+  </si>
+  <si>
+    <t>Ron Weasley</t>
+  </si>
+  <si>
+    <t>Team Sigma</t>
+  </si>
+  <si>
+    <t>WEASLEY</t>
+  </si>
+  <si>
+    <t>K15</t>
+  </si>
+  <si>
+    <t>Samwise Gamgee</t>
+  </si>
+  <si>
+    <t>Team Tau</t>
+  </si>
+  <si>
+    <t>GAMGEE</t>
+  </si>
+  <si>
+    <t>K16</t>
+  </si>
+  <si>
     <t>Daenerys Targaryen</t>
   </si>
   <si>
@@ -101,7 +272,76 @@
     <t>TARGARYEN</t>
   </si>
   <si>
-    <t>K2</t>
+    <t>K17</t>
+  </si>
+  <si>
+    <t>Tyrion Lannister</t>
+  </si>
+  <si>
+    <t>Team Upsilon</t>
+  </si>
+  <si>
+    <t>K18</t>
+  </si>
+  <si>
+    <t>Ulysses</t>
+  </si>
+  <si>
+    <t>Team Phi</t>
+  </si>
+  <si>
+    <t>ULYSSES</t>
+  </si>
+  <si>
+    <t>K19</t>
+  </si>
+  <si>
+    <t>Voldemort</t>
+  </si>
+  <si>
+    <t>Team Chi</t>
+  </si>
+  <si>
+    <t>VOLDEMORT</t>
+  </si>
+  <si>
+    <t>K20</t>
+  </si>
+  <si>
+    <t>Willy Wonka</t>
+  </si>
+  <si>
+    <t>Team Psi</t>
+  </si>
+  <si>
+    <t>WONKA</t>
+  </si>
+  <si>
+    <t>K21</t>
+  </si>
+  <si>
+    <t>Xaro Xhoan Daxos</t>
+  </si>
+  <si>
+    <t>Team Omega</t>
+  </si>
+  <si>
+    <t>DAXOS</t>
+  </si>
+  <si>
+    <t>K22</t>
+  </si>
+  <si>
+    <t>Ygritte</t>
+  </si>
+  <si>
+    <t>Team Alpha</t>
+  </si>
+  <si>
+    <t>YGRITTE</t>
+  </si>
+  <si>
+    <t>K23</t>
   </si>
   <si>
     <t>Eddard Stark</t>
@@ -111,246 +351,6 @@
   </si>
   <si>
     <t>STARK</t>
-  </si>
-  <si>
-    <t>K3</t>
-  </si>
-  <si>
-    <t>Frodo Baggins</t>
-  </si>
-  <si>
-    <t>Team Zeta</t>
-  </si>
-  <si>
-    <t>BAGGINS</t>
-  </si>
-  <si>
-    <t>K4</t>
-  </si>
-  <si>
-    <t>Gandalf The Grey</t>
-  </si>
-  <si>
-    <t>Team Eta</t>
-  </si>
-  <si>
-    <t>GANDALF</t>
-  </si>
-  <si>
-    <t>K5</t>
-  </si>
-  <si>
-    <t>Hermione Granger</t>
-  </si>
-  <si>
-    <t>Team Theta</t>
-  </si>
-  <si>
-    <t>GRANGER</t>
-  </si>
-  <si>
-    <t>K6</t>
-  </si>
-  <si>
-    <t>Inigo Montoya</t>
-  </si>
-  <si>
-    <t>Team Iota</t>
-  </si>
-  <si>
-    <t>MONTOYA</t>
-  </si>
-  <si>
-    <t>K7</t>
-  </si>
-  <si>
-    <t>Jon Snow</t>
-  </si>
-  <si>
-    <t>Team Kappa</t>
-  </si>
-  <si>
-    <t>SNOW</t>
-  </si>
-  <si>
-    <t>K8</t>
-  </si>
-  <si>
-    <t>Katniss Everdeen</t>
-  </si>
-  <si>
-    <t>Team Lambda</t>
-  </si>
-  <si>
-    <t>EVERDEEN</t>
-  </si>
-  <si>
-    <t>K9</t>
-  </si>
-  <si>
-    <t>Team Mu</t>
-  </si>
-  <si>
-    <t>K10</t>
-  </si>
-  <si>
-    <t>Legolas Greenleaf</t>
-  </si>
-  <si>
-    <t>GREENLEAF</t>
-  </si>
-  <si>
-    <t>K11</t>
-  </si>
-  <si>
-    <t>Moby Dick</t>
-  </si>
-  <si>
-    <t>Team Nu</t>
-  </si>
-  <si>
-    <t>DICK</t>
-  </si>
-  <si>
-    <t>K12</t>
-  </si>
-  <si>
-    <t>Neville Longbottom</t>
-  </si>
-  <si>
-    <t>Team Xi</t>
-  </si>
-  <si>
-    <t>LONGBOTTOM</t>
-  </si>
-  <si>
-    <t>K13</t>
-  </si>
-  <si>
-    <t>Othello</t>
-  </si>
-  <si>
-    <t>Team Omicron</t>
-  </si>
-  <si>
-    <t>OTHELLO</t>
-  </si>
-  <si>
-    <t>K14</t>
-  </si>
-  <si>
-    <t>Petyr Baelish</t>
-  </si>
-  <si>
-    <t>Team Pi</t>
-  </si>
-  <si>
-    <t>BAELISH</t>
-  </si>
-  <si>
-    <t>K15</t>
-  </si>
-  <si>
-    <t>Quirinus Quirrell</t>
-  </si>
-  <si>
-    <t>Team Rho</t>
-  </si>
-  <si>
-    <t>QUIRRELL</t>
-  </si>
-  <si>
-    <t>K16</t>
-  </si>
-  <si>
-    <t>Ron Weasley</t>
-  </si>
-  <si>
-    <t>Team Sigma</t>
-  </si>
-  <si>
-    <t>WEASLEY</t>
-  </si>
-  <si>
-    <t>K17</t>
-  </si>
-  <si>
-    <t>Samwise Gamgee</t>
-  </si>
-  <si>
-    <t>Team Tau</t>
-  </si>
-  <si>
-    <t>GAMGEE</t>
-  </si>
-  <si>
-    <t>K18</t>
-  </si>
-  <si>
-    <t>Tyrion Lannister</t>
-  </si>
-  <si>
-    <t>Team Upsilon</t>
-  </si>
-  <si>
-    <t>K19</t>
-  </si>
-  <si>
-    <t>Ulysses</t>
-  </si>
-  <si>
-    <t>Team Phi</t>
-  </si>
-  <si>
-    <t>ULYSSES</t>
-  </si>
-  <si>
-    <t>K20</t>
-  </si>
-  <si>
-    <t>Voldemort</t>
-  </si>
-  <si>
-    <t>Team Chi</t>
-  </si>
-  <si>
-    <t>VOLDEMORT</t>
-  </si>
-  <si>
-    <t>K21</t>
-  </si>
-  <si>
-    <t>Willy Wonka</t>
-  </si>
-  <si>
-    <t>Team Psi</t>
-  </si>
-  <si>
-    <t>WONKA</t>
-  </si>
-  <si>
-    <t>K22</t>
-  </si>
-  <si>
-    <t>Xaro Xhoan Daxos</t>
-  </si>
-  <si>
-    <t>Team Omega</t>
-  </si>
-  <si>
-    <t>DAXOS</t>
-  </si>
-  <si>
-    <t>K23</t>
-  </si>
-  <si>
-    <t>Ygritte</t>
-  </si>
-  <si>
-    <t>Team Alpha</t>
-  </si>
-  <si>
-    <t>YGRITTE</t>
   </si>
   <si>
     <t>K24</t>
@@ -1045,7 +1045,7 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
@@ -1062,7 +1062,7 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
@@ -1079,7 +1079,7 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>29</v>
@@ -1096,7 +1096,7 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>33</v>
@@ -1113,7 +1113,7 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
         <v>37</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B9" t="s">
         <v>41</v>
@@ -1147,7 +1147,7 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
         <v>45</v>
@@ -1164,7 +1164,7 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B11" t="s">
         <v>49</v>
@@ -1181,67 +1181,67 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D12" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E12" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D13" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C14" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D14" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E14" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="C15" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="D15" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="E15" t="s">
         <v>65</v>
@@ -1249,7 +1249,7 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
         <v>66</v>
@@ -1266,7 +1266,7 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
         <v>70</v>
@@ -1283,7 +1283,7 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B18" t="s">
         <v>74</v>
@@ -1300,7 +1300,7 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="B19" t="s">
         <v>78</v>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" t="s">
         <v>82</v>
@@ -1326,24 +1326,24 @@
         <v>83</v>
       </c>
       <c r="D20" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" t="s">
         <v>84</v>
-      </c>
-      <c r="E20" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21" t="s">
         <v>86</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>87</v>
-      </c>
-      <c r="D21" t="s">
-        <v>19</v>
       </c>
       <c r="E21" t="s">
         <v>88</v>
@@ -1351,7 +1351,7 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" t="s">
         <v>89</v>
@@ -1368,7 +1368,7 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23" t="s">
         <v>93</v>
@@ -1385,7 +1385,7 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" t="s">
         <v>97</v>
@@ -1402,7 +1402,7 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25" t="s">
         <v>101</v>
@@ -1419,7 +1419,7 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="B26" t="s">
         <v>105</v>
@@ -1458,90 +1458,90 @@
     </row>
     <row r="2" ht="270" customHeight="true">
       <c r="A2" s="17" t="str">
-        <f>'data'!$E$7</f>
+        <f>'data'!$E$4</f>
       </c>
       <c r="B2" s="18" t="str">
-        <f>'data'!D7</f>
+        <f>'data'!D4</f>
       </c>
     </row>
     <row r="3" ht="270" customHeight="true">
       <c r="A3" s="17" t="str">
-        <f>'data'!$E$8</f>
+        <f>'data'!$E$5</f>
       </c>
       <c r="B3" s="18" t="str">
-        <f>'data'!D8</f>
+        <f>'data'!D5</f>
       </c>
     </row>
     <row r="4" ht="270" customHeight="true">
       <c r="A4" s="17" t="str">
-        <f>'data'!$E$9</f>
+        <f>'data'!$E$6</f>
       </c>
       <c r="B4" s="18" t="str">
-        <f>'data'!D9</f>
+        <f>'data'!D6</f>
       </c>
     </row>
     <row r="5" ht="270" customHeight="true">
       <c r="A5" s="17" t="str">
-        <f>'data'!$E$10</f>
+        <f>'data'!$E$7</f>
       </c>
       <c r="B5" s="18" t="str">
-        <f>'data'!D10</f>
+        <f>'data'!D7</f>
       </c>
     </row>
     <row r="6" ht="270" customHeight="true">
       <c r="A6" s="17" t="str">
-        <f>'data'!$E$11</f>
+        <f>'data'!$E$8</f>
       </c>
       <c r="B6" s="18" t="str">
-        <f>'data'!D11</f>
+        <f>'data'!D8</f>
       </c>
     </row>
     <row r="7" ht="270" customHeight="true">
       <c r="A7" s="17" t="str">
-        <f>'data'!$E$17</f>
+        <f>'data'!$E$9</f>
       </c>
       <c r="B7" s="18" t="str">
-        <f>'data'!D17</f>
+        <f>'data'!D9</f>
       </c>
     </row>
     <row r="8" ht="270" customHeight="true">
       <c r="A8" s="17" t="str">
-        <f>'data'!$E$13</f>
+        <f>'data'!$E$10</f>
       </c>
       <c r="B8" s="18" t="str">
-        <f>'data'!D13</f>
+        <f>'data'!D10</f>
       </c>
     </row>
     <row r="9" ht="270" customHeight="true">
       <c r="A9" s="17" t="str">
-        <f>'data'!$E$6</f>
+        <f>'data'!$E$11</f>
       </c>
       <c r="B9" s="18" t="str">
-        <f>'data'!D6</f>
+        <f>'data'!D11</f>
       </c>
     </row>
     <row r="10" ht="270" customHeight="true">
       <c r="A10" s="17" t="str">
-        <f>'data'!$E$14</f>
+        <f>'data'!$E$12</f>
       </c>
       <c r="B10" s="18" t="str">
-        <f>'data'!D14</f>
+        <f>'data'!D12</f>
       </c>
     </row>
     <row r="11" ht="270" customHeight="true">
       <c r="A11" s="17" t="str">
-        <f>'data'!$E$15</f>
+        <f>'data'!$E$13</f>
       </c>
       <c r="B11" s="18" t="str">
-        <f>'data'!D15</f>
+        <f>'data'!D13</f>
       </c>
     </row>
     <row r="12" ht="270" customHeight="true">
       <c r="A12" s="17" t="str">
-        <f>'data'!$E$16</f>
+        <f>'data'!$E$14</f>
       </c>
       <c r="B12" s="18" t="str">
-        <f>'data'!D16</f>
+        <f>'data'!D14</f>
       </c>
     </row>
   </sheetData>
@@ -1568,98 +1568,98 @@
   <sheetData>
     <row r="1" ht="270" customHeight="true">
       <c r="A1" s="17" t="str">
-        <f>'data'!$E$12</f>
+        <f>'data'!$E$15</f>
       </c>
       <c r="B1" s="18" t="str">
-        <f>'data'!D12</f>
+        <f>'data'!D15</f>
       </c>
     </row>
     <row r="2" ht="270" customHeight="true">
       <c r="A2" s="17" t="str">
-        <f>'data'!$E$18</f>
+        <f>'data'!$E$16</f>
       </c>
       <c r="B2" s="18" t="str">
-        <f>'data'!D18</f>
+        <f>'data'!D16</f>
       </c>
     </row>
     <row r="3" ht="270" customHeight="true">
       <c r="A3" s="17" t="str">
-        <f>'data'!$E$19</f>
+        <f>'data'!$E$17</f>
       </c>
       <c r="B3" s="18" t="str">
-        <f>'data'!D19</f>
+        <f>'data'!D17</f>
       </c>
     </row>
     <row r="4" ht="270" customHeight="true">
       <c r="A4" s="17" t="str">
-        <f>'data'!$E$20</f>
+        <f>'data'!$E$18</f>
       </c>
       <c r="B4" s="18" t="str">
-        <f>'data'!D20</f>
+        <f>'data'!D18</f>
       </c>
     </row>
     <row r="5" ht="270" customHeight="true">
       <c r="A5" s="17" t="str">
-        <f>'data'!$E$4</f>
+        <f>'data'!$E$19</f>
       </c>
       <c r="B5" s="18" t="str">
-        <f>'data'!D4</f>
+        <f>'data'!D19</f>
       </c>
     </row>
     <row r="6" ht="270" customHeight="true">
       <c r="A6" s="17" t="str">
-        <f>'data'!$E$21</f>
+        <f>'data'!$E$20</f>
       </c>
       <c r="B6" s="18" t="str">
-        <f>'data'!D21</f>
+        <f>'data'!D20</f>
       </c>
     </row>
     <row r="7" ht="270" customHeight="true">
       <c r="A7" s="17" t="str">
-        <f>'data'!$E$22</f>
+        <f>'data'!$E$21</f>
       </c>
       <c r="B7" s="18" t="str">
-        <f>'data'!D22</f>
+        <f>'data'!D21</f>
       </c>
     </row>
     <row r="8" ht="270" customHeight="true">
       <c r="A8" s="17" t="str">
-        <f>'data'!$E$23</f>
+        <f>'data'!$E$22</f>
       </c>
       <c r="B8" s="18" t="str">
-        <f>'data'!D23</f>
+        <f>'data'!D22</f>
       </c>
     </row>
     <row r="9" ht="270" customHeight="true">
       <c r="A9" s="17" t="str">
-        <f>'data'!$E$24</f>
+        <f>'data'!$E$23</f>
       </c>
       <c r="B9" s="18" t="str">
-        <f>'data'!D24</f>
+        <f>'data'!D23</f>
       </c>
     </row>
     <row r="10" ht="270" customHeight="true">
       <c r="A10" s="17" t="str">
-        <f>'data'!$E$25</f>
+        <f>'data'!$E$24</f>
       </c>
       <c r="B10" s="18" t="str">
-        <f>'data'!D25</f>
+        <f>'data'!D24</f>
       </c>
     </row>
     <row r="11" ht="270" customHeight="true">
       <c r="A11" s="17" t="str">
-        <f>'data'!$E$26</f>
+        <f>'data'!$E$25</f>
       </c>
       <c r="B11" s="18" t="str">
-        <f>'data'!D26</f>
+        <f>'data'!D25</f>
       </c>
     </row>
     <row r="12" ht="270" customHeight="true">
       <c r="A12" s="17" t="str">
-        <f>'data'!$E$5</f>
+        <f>'data'!$E$26</f>
       </c>
       <c r="B12" s="18" t="str">
-        <f>'data'!D5</f>
+        <f>'data'!D26</f>
       </c>
     </row>
   </sheetData>
@@ -2033,7 +2033,7 @@
     </row>
     <row r="4">
       <c r="A4" s="19" t="str">
-        <f>'data'!$B$8</f>
+        <f>'data'!$B$5</f>
       </c>
       <c r="B4" s="22"/>
       <c r="C4" s="22"/>
@@ -2041,10 +2041,10 @@
       <c r="E4" s="22"/>
       <c r="F4" s="22"/>
       <c r="G4" s="19" t="str">
-        <f>'data'!$B$7</f>
+        <f>'data'!$B$4</f>
       </c>
       <c r="I4" s="19" t="str">
-        <f>'data'!$B$19</f>
+        <f>'data'!$B$17</f>
       </c>
       <c r="J4" s="22"/>
       <c r="K4" s="22"/>
@@ -2052,7 +2052,7 @@
       <c r="M4" s="22"/>
       <c r="N4" s="22"/>
       <c r="O4" s="19" t="str">
-        <f>'data'!$B$18</f>
+        <f>'data'!$B$16</f>
       </c>
     </row>
     <row r="6">
@@ -2117,7 +2117,7 @@
     </row>
     <row r="12">
       <c r="A12" s="19" t="str">
-        <f>'data'!$B$12</f>
+        <f>'data'!$B$15</f>
       </c>
       <c r="B12" s="22"/>
       <c r="C12" s="22"/>
@@ -2125,10 +2125,10 @@
       <c r="E12" s="22"/>
       <c r="F12" s="22"/>
       <c r="G12" s="19" t="str">
-        <f>'data'!$B$10</f>
+        <f>'data'!$B$7</f>
       </c>
       <c r="I12" s="19" t="str">
-        <f>'data'!$B$21</f>
+        <f>'data'!$B$20</f>
       </c>
       <c r="J12" s="22"/>
       <c r="K12" s="22"/>
@@ -2136,7 +2136,7 @@
       <c r="M12" s="22"/>
       <c r="N12" s="22"/>
       <c r="O12" s="19" t="str">
-        <f>'data'!$B$4</f>
+        <f>'data'!$B$19</f>
       </c>
     </row>
     <row r="14">
@@ -2201,7 +2201,7 @@
     </row>
     <row r="20">
       <c r="A20" s="19" t="str">
-        <f>'data'!$B$6</f>
+        <f>'data'!$B$11</f>
       </c>
       <c r="B20" s="22"/>
       <c r="C20" s="22"/>
@@ -2209,10 +2209,10 @@
       <c r="E20" s="22"/>
       <c r="F20" s="22"/>
       <c r="G20" s="19" t="str">
-        <f>'data'!$B$13</f>
+        <f>'data'!$B$10</f>
       </c>
       <c r="I20" s="19" t="str">
-        <f>'data'!$B$24</f>
+        <f>'data'!$B$23</f>
       </c>
       <c r="J20" s="22"/>
       <c r="K20" s="22"/>
@@ -2220,7 +2220,7 @@
       <c r="M20" s="22"/>
       <c r="N20" s="22"/>
       <c r="O20" s="19" t="str">
-        <f>'data'!$B$23</f>
+        <f>'data'!$B$22</f>
       </c>
     </row>
     <row r="22">
@@ -2285,7 +2285,7 @@
     </row>
     <row r="28">
       <c r="A28" s="19" t="str">
-        <f>'data'!$B$16</f>
+        <f>'data'!$B$14</f>
       </c>
       <c r="B28" s="22"/>
       <c r="C28" s="22"/>
@@ -2293,10 +2293,10 @@
       <c r="E28" s="22"/>
       <c r="F28" s="22"/>
       <c r="G28" s="19" t="str">
-        <f>'data'!$B$15</f>
+        <f>'data'!$B$13</f>
       </c>
       <c r="I28" s="19" t="str">
-        <f>'data'!$B$5</f>
+        <f>'data'!$B$26</f>
       </c>
       <c r="J28" s="22"/>
       <c r="K28" s="22"/>
@@ -2304,7 +2304,7 @@
       <c r="M28" s="22"/>
       <c r="N28" s="22"/>
       <c r="O28" s="19" t="str">
-        <f>'data'!$B$26</f>
+        <f>'data'!$B$25</f>
       </c>
     </row>
     <row r="30">
@@ -2377,7 +2377,7 @@
       <c r="E41" s="22"/>
       <c r="F41" s="22"/>
       <c r="G41" s="19" t="str">
-        <f>'data'!$B$21</f>
+        <f>'data'!$B$20</f>
       </c>
       <c r="I41" s="19" t="str">
         <f>CONCATENATE("M 5 ",O6)</f>
@@ -2388,7 +2388,7 @@
       <c r="M41" s="22"/>
       <c r="N41" s="22"/>
       <c r="O41" s="19" t="str">
-        <f>'data'!$B$12</f>
+        <f>'data'!$B$15</f>
       </c>
     </row>
     <row r="43">
@@ -2461,7 +2461,7 @@
       <c r="E49" s="22"/>
       <c r="F49" s="22"/>
       <c r="G49" s="19" t="str">
-        <f>'data'!$B$9</f>
+        <f>'data'!$B$6</f>
       </c>
       <c r="I49" s="19" t="str">
         <f>CONCATENATE("M 6 ",O14)</f>
@@ -2472,7 +2472,7 @@
       <c r="M49" s="22"/>
       <c r="N49" s="22"/>
       <c r="O49" s="19" t="str">
-        <f>'data'!$B$20</f>
+        <f>'data'!$B$18</f>
       </c>
     </row>
     <row r="51">
@@ -2545,7 +2545,7 @@
       <c r="E57" s="22"/>
       <c r="F57" s="22"/>
       <c r="G57" s="19" t="str">
-        <f>'data'!$B$17</f>
+        <f>'data'!$B$9</f>
       </c>
       <c r="I57" s="19" t="str">
         <f>CONCATENATE("M 7 ",O22)</f>
@@ -2556,7 +2556,7 @@
       <c r="M57" s="22"/>
       <c r="N57" s="22"/>
       <c r="O57" s="19" t="str">
-        <f>'data'!$B$22</f>
+        <f>'data'!$B$21</f>
       </c>
     </row>
     <row r="59">
@@ -2629,7 +2629,7 @@
       <c r="E65" s="22"/>
       <c r="F65" s="22"/>
       <c r="G65" s="19" t="str">
-        <f>'data'!$B$14</f>
+        <f>'data'!$B$12</f>
       </c>
       <c r="I65" s="19" t="str">
         <f>CONCATENATE("M 8 ",O30)</f>
@@ -2640,7 +2640,7 @@
       <c r="M65" s="22"/>
       <c r="N65" s="22"/>
       <c r="O65" s="19" t="str">
-        <f>'data'!$B$25</f>
+        <f>'data'!$B$24</f>
       </c>
     </row>
     <row r="67">
@@ -3050,7 +3050,7 @@
     </row>
     <row r="9">
       <c r="C9" s="16" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="G9" s="12"/>
       <c r="H9" s="14"/>
@@ -3067,7 +3067,7 @@
     </row>
     <row r="11">
       <c r="C11" s="16" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="12"/>
@@ -3087,7 +3087,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -3108,7 +3108,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -3124,7 +3124,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -3142,7 +3142,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="K22" s="12"/>
     </row>
@@ -3159,7 +3159,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -3178,7 +3178,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -3199,7 +3199,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -3217,7 +3217,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -3231,7 +3231,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>
@@ -3279,7 +3279,7 @@
       <c r="C6" s="16"/>
       <c r="D6" s="16"/>
       <c r="E6" s="16" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
@@ -3293,7 +3293,7 @@
     </row>
     <row r="9">
       <c r="C9" s="16" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G9" s="12"/>
       <c r="H9" s="14"/>
@@ -3310,7 +3310,7 @@
     </row>
     <row r="11">
       <c r="C11" s="16" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="12"/>
@@ -3330,7 +3330,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -3351,7 +3351,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -3385,7 +3385,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="K22" s="12"/>
     </row>
@@ -3402,7 +3402,7 @@
     </row>
     <row r="25">
       <c r="C25" s="16" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="14"/>
@@ -3421,7 +3421,7 @@
     </row>
     <row r="27">
       <c r="C27" s="16" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="12"/>
@@ -3442,7 +3442,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -3460,7 +3460,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -3474,7 +3474,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>27</v>
+        <v>107</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>
